--- a/template.xlsx
+++ b/template.xlsx
@@ -450,7 +450,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -514,7 +514,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="60" fontId="5" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="60" fontId="5" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -542,6 +542,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="60" fontId="5" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -1679,7 +1682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:W12"/>
+  <dimension ref="A1:W55"/>
   <sheetFormatPr defaultColWidth="10.8333" defaultRowHeight="14" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="10.8516" style="1" customWidth="1"/>
@@ -1918,47 +1921,23 @@
       <c r="W7" s="4"/>
     </row>
     <row r="8" ht="21.85" customHeight="1">
-      <c r="A8" s="31"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="33" cm="1">
-        <f t="array" ref="F8">SUM(F7:F7)</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="34" cm="1">
-        <f t="array" ref="G8">SUM(G7:G7)</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="32"/>
-      <c r="I8" s="34" cm="1">
-        <f t="array" ref="I8">SUM(I7:I7)</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="35" cm="1">
-        <f t="array" ref="J8">SUM(J7:J7)</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="34" cm="1">
-        <f t="array" ref="K8">SUM(K7:K7)</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="33" cm="1">
-        <f t="array" ref="L8">SUM(L7:L7)</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="36" cm="1">
-        <f t="array" ref="M8">SUM(M7:M7)</f>
-        <v>0</v>
-      </c>
-      <c r="N8" s="37" cm="1">
-        <f t="array" ref="N8">SUM(G8+I8+K8+M8)</f>
-        <v>0</v>
-      </c>
-      <c r="O8" s="32"/>
-      <c r="P8" s="32"/>
-      <c r="Q8" s="19"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="30"/>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
@@ -1967,25 +1946,23 @@
       <c r="W8" s="4"/>
     </row>
     <row r="9" ht="21.85" customHeight="1">
-      <c r="A9" s="38"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" t="s" s="40">
-        <v>19</v>
-      </c>
-      <c r="E9" s="41"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="43"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="39"/>
-      <c r="P9" s="39"/>
-      <c r="Q9" s="4"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="30"/>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
       <c r="T9" s="4"/>
@@ -1994,13 +1971,11 @@
       <c r="W9" s="4"/>
     </row>
     <row r="10" ht="21.85" customHeight="1">
-      <c r="A10" s="31"/>
-      <c r="B10" s="44"/>
-      <c r="C10" s="22"/>
-      <c r="D10" t="s" s="45">
-        <v>20</v>
-      </c>
-      <c r="E10" s="46"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="23"/>
       <c r="F10" s="22"/>
       <c r="G10" s="22"/>
       <c r="H10" s="22"/>
@@ -2010,14 +1985,9 @@
       <c r="L10" s="22"/>
       <c r="M10" s="26"/>
       <c r="N10" s="27"/>
-      <c r="O10" t="s" s="23">
-        <v>21</v>
-      </c>
-      <c r="P10" s="47" cm="1">
-        <f t="array" ref="P10">SUM(F8,J8,L8)</f>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="19"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="30"/>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
       <c r="T10" s="4"/>
@@ -2026,11 +1996,11 @@
       <c r="W10" s="4"/>
     </row>
     <row r="11" ht="21.85" customHeight="1">
-      <c r="A11" s="31"/>
-      <c r="B11" s="44"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="46"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="23"/>
       <c r="F11" s="22"/>
       <c r="G11" s="22"/>
       <c r="H11" s="22"/>
@@ -2040,14 +2010,9 @@
       <c r="L11" s="22"/>
       <c r="M11" s="26"/>
       <c r="N11" s="27"/>
-      <c r="O11" t="s" s="23">
-        <v>22</v>
-      </c>
-      <c r="P11" s="47" cm="1">
-        <f t="array" ref="P11">SUM(G8+K8+M8)</f>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="19"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="30"/>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
       <c r="T11" s="4"/>
@@ -2055,32 +2020,24 @@
       <c r="V11" s="4"/>
       <c r="W11" s="4"/>
     </row>
-    <row r="12" ht="148.75" customHeight="1">
-      <c r="A12" t="s" s="48">
-        <v>23</v>
-      </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" t="s" s="50">
-        <v>24</v>
-      </c>
-      <c r="E12" t="s" s="51">
-        <v>25</v>
-      </c>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" t="s" s="54">
-        <v>26</v>
-      </c>
-      <c r="K12" s="53"/>
-      <c r="L12" s="53"/>
-      <c r="M12" s="55"/>
-      <c r="N12" s="53"/>
-      <c r="O12" s="53"/>
-      <c r="P12" s="53"/>
-      <c r="Q12" s="4"/>
+    <row r="12" ht="21.85" customHeight="1">
+      <c r="A12" s="21"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="30"/>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
       <c r="T12" s="4"/>
@@ -2088,12 +2045,1133 @@
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
     </row>
+    <row r="13" ht="21.85" customHeight="1">
+      <c r="A13" s="21"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="30"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+    </row>
+    <row r="14" ht="21.85" customHeight="1">
+      <c r="A14" s="21"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="30"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+    </row>
+    <row r="15" ht="21.85" customHeight="1">
+      <c r="A15" s="21"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="30"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="4"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="4"/>
+    </row>
+    <row r="16" ht="21.85" customHeight="1">
+      <c r="A16" s="21"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="30"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4"/>
+    </row>
+    <row r="17" ht="21.85" customHeight="1">
+      <c r="A17" s="21"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="30"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+    </row>
+    <row r="18" ht="21.85" customHeight="1">
+      <c r="A18" s="21"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="27"/>
+      <c r="O18" s="28"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="30"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
+    </row>
+    <row r="19" ht="21.85" customHeight="1">
+      <c r="A19" s="21"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="29"/>
+      <c r="Q19" s="30"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+    </row>
+    <row r="20" ht="21.85" customHeight="1">
+      <c r="A20" s="21"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="4"/>
+    </row>
+    <row r="21" ht="21.85" customHeight="1">
+      <c r="A21" s="21"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="26"/>
+      <c r="N21" s="27"/>
+      <c r="O21" s="28"/>
+      <c r="P21" s="29"/>
+      <c r="Q21" s="30"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="4"/>
+    </row>
+    <row r="22" ht="21.85" customHeight="1">
+      <c r="A22" s="21"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="29"/>
+      <c r="Q22" s="30"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="4"/>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="4"/>
+    </row>
+    <row r="23" ht="21.85" customHeight="1">
+      <c r="A23" s="21"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="27"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="4"/>
+    </row>
+    <row r="24" ht="21.85" customHeight="1">
+      <c r="A24" s="21"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="27"/>
+      <c r="O24" s="28"/>
+      <c r="P24" s="29"/>
+      <c r="Q24" s="30"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="4"/>
+    </row>
+    <row r="25" ht="21.85" customHeight="1">
+      <c r="A25" s="21"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="27"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="30"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="4"/>
+    </row>
+    <row r="26" ht="21.85" customHeight="1">
+      <c r="A26" s="21"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="27"/>
+      <c r="O26" s="28"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="4"/>
+    </row>
+    <row r="27" ht="21.85" customHeight="1">
+      <c r="A27" s="21"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="27"/>
+      <c r="O27" s="28"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="30"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="4"/>
+      <c r="T27" s="4"/>
+      <c r="U27" s="4"/>
+      <c r="V27" s="4"/>
+      <c r="W27" s="4"/>
+    </row>
+    <row r="28" ht="21.85" customHeight="1">
+      <c r="A28" s="21"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="27"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="29"/>
+      <c r="Q28" s="30"/>
+      <c r="R28" s="4"/>
+      <c r="S28" s="4"/>
+      <c r="T28" s="4"/>
+      <c r="U28" s="4"/>
+      <c r="V28" s="4"/>
+      <c r="W28" s="4"/>
+    </row>
+    <row r="29" ht="21.85" customHeight="1">
+      <c r="A29" s="21"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="27"/>
+      <c r="O29" s="28"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="4"/>
+      <c r="S29" s="4"/>
+      <c r="T29" s="4"/>
+      <c r="U29" s="4"/>
+      <c r="V29" s="4"/>
+      <c r="W29" s="4"/>
+    </row>
+    <row r="30" ht="21.85" customHeight="1">
+      <c r="A30" s="21"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="27"/>
+      <c r="O30" s="28"/>
+      <c r="P30" s="29"/>
+      <c r="Q30" s="30"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="4"/>
+      <c r="T30" s="4"/>
+      <c r="U30" s="4"/>
+      <c r="V30" s="4"/>
+      <c r="W30" s="4"/>
+    </row>
+    <row r="31" ht="21.85" customHeight="1">
+      <c r="A31" s="21"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="27"/>
+      <c r="O31" s="28"/>
+      <c r="P31" s="29"/>
+      <c r="Q31" s="30"/>
+      <c r="R31" s="4"/>
+      <c r="S31" s="4"/>
+      <c r="T31" s="4"/>
+      <c r="U31" s="4"/>
+      <c r="V31" s="4"/>
+      <c r="W31" s="4"/>
+    </row>
+    <row r="32" ht="21.85" customHeight="1">
+      <c r="A32" s="21"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="27"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="29"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="4"/>
+      <c r="S32" s="4"/>
+      <c r="T32" s="4"/>
+      <c r="U32" s="4"/>
+      <c r="V32" s="4"/>
+      <c r="W32" s="4"/>
+    </row>
+    <row r="33" ht="21.85" customHeight="1">
+      <c r="A33" s="21"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="27"/>
+      <c r="O33" s="28"/>
+      <c r="P33" s="29"/>
+      <c r="Q33" s="30"/>
+      <c r="R33" s="4"/>
+      <c r="S33" s="4"/>
+      <c r="T33" s="4"/>
+      <c r="U33" s="4"/>
+      <c r="V33" s="4"/>
+      <c r="W33" s="4"/>
+    </row>
+    <row r="34" ht="21.85" customHeight="1">
+      <c r="A34" s="21"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="27"/>
+      <c r="O34" s="28"/>
+      <c r="P34" s="29"/>
+      <c r="Q34" s="30"/>
+      <c r="R34" s="4"/>
+      <c r="S34" s="4"/>
+      <c r="T34" s="4"/>
+      <c r="U34" s="4"/>
+      <c r="V34" s="4"/>
+      <c r="W34" s="4"/>
+    </row>
+    <row r="35" ht="21.85" customHeight="1">
+      <c r="A35" s="21"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="27"/>
+      <c r="O35" s="28"/>
+      <c r="P35" s="29"/>
+      <c r="Q35" s="30"/>
+      <c r="R35" s="4"/>
+      <c r="S35" s="4"/>
+      <c r="T35" s="4"/>
+      <c r="U35" s="4"/>
+      <c r="V35" s="4"/>
+      <c r="W35" s="4"/>
+    </row>
+    <row r="36" ht="21.85" customHeight="1">
+      <c r="A36" s="21"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="26"/>
+      <c r="N36" s="27"/>
+      <c r="O36" s="28"/>
+      <c r="P36" s="29"/>
+      <c r="Q36" s="30"/>
+      <c r="R36" s="4"/>
+      <c r="S36" s="4"/>
+      <c r="T36" s="4"/>
+      <c r="U36" s="4"/>
+      <c r="V36" s="4"/>
+      <c r="W36" s="4"/>
+    </row>
+    <row r="37" ht="21.85" customHeight="1">
+      <c r="A37" s="21"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="25"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="27"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="29"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="4"/>
+      <c r="S37" s="4"/>
+      <c r="T37" s="4"/>
+      <c r="U37" s="4"/>
+      <c r="V37" s="4"/>
+      <c r="W37" s="4"/>
+    </row>
+    <row r="38" ht="21.85" customHeight="1">
+      <c r="A38" s="21"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="25"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="25"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="26"/>
+      <c r="N38" s="27"/>
+      <c r="O38" s="28"/>
+      <c r="P38" s="29"/>
+      <c r="Q38" s="30"/>
+      <c r="R38" s="4"/>
+      <c r="S38" s="4"/>
+      <c r="T38" s="4"/>
+      <c r="U38" s="4"/>
+      <c r="V38" s="4"/>
+      <c r="W38" s="4"/>
+    </row>
+    <row r="39" ht="21.85" customHeight="1">
+      <c r="A39" s="21"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="25"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="26"/>
+      <c r="N39" s="27"/>
+      <c r="O39" s="28"/>
+      <c r="P39" s="29"/>
+      <c r="Q39" s="30"/>
+      <c r="R39" s="4"/>
+      <c r="S39" s="4"/>
+      <c r="T39" s="4"/>
+      <c r="U39" s="4"/>
+      <c r="V39" s="4"/>
+      <c r="W39" s="4"/>
+    </row>
+    <row r="40" ht="21.85" customHeight="1">
+      <c r="A40" s="21"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="I40" s="25"/>
+      <c r="J40" s="22"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="26"/>
+      <c r="N40" s="27"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="29"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="4"/>
+      <c r="T40" s="4"/>
+      <c r="U40" s="4"/>
+      <c r="V40" s="4"/>
+      <c r="W40" s="4"/>
+    </row>
+    <row r="41" ht="21.85" customHeight="1">
+      <c r="A41" s="21"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="25"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="25"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="26"/>
+      <c r="N41" s="27"/>
+      <c r="O41" s="28"/>
+      <c r="P41" s="29"/>
+      <c r="Q41" s="30"/>
+      <c r="R41" s="4"/>
+      <c r="S41" s="4"/>
+      <c r="T41" s="4"/>
+      <c r="U41" s="4"/>
+      <c r="V41" s="4"/>
+      <c r="W41" s="4"/>
+    </row>
+    <row r="42" ht="21.85" customHeight="1">
+      <c r="A42" s="21"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="25"/>
+      <c r="J42" s="22"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="27"/>
+      <c r="O42" s="28"/>
+      <c r="P42" s="29"/>
+      <c r="Q42" s="30"/>
+      <c r="R42" s="4"/>
+      <c r="S42" s="4"/>
+      <c r="T42" s="4"/>
+      <c r="U42" s="4"/>
+      <c r="V42" s="4"/>
+      <c r="W42" s="4"/>
+    </row>
+    <row r="43" ht="21.85" customHeight="1">
+      <c r="A43" s="21"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="25"/>
+      <c r="J43" s="22"/>
+      <c r="K43" s="25"/>
+      <c r="L43" s="22"/>
+      <c r="M43" s="26"/>
+      <c r="N43" s="27"/>
+      <c r="O43" s="28"/>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="4"/>
+      <c r="S43" s="4"/>
+      <c r="T43" s="4"/>
+      <c r="U43" s="4"/>
+      <c r="V43" s="4"/>
+      <c r="W43" s="4"/>
+    </row>
+    <row r="44" ht="21.85" customHeight="1">
+      <c r="A44" s="21"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="25"/>
+      <c r="J44" s="22"/>
+      <c r="K44" s="25"/>
+      <c r="L44" s="22"/>
+      <c r="M44" s="26"/>
+      <c r="N44" s="27"/>
+      <c r="O44" s="28"/>
+      <c r="P44" s="29"/>
+      <c r="Q44" s="30"/>
+      <c r="R44" s="4"/>
+      <c r="S44" s="4"/>
+      <c r="T44" s="4"/>
+      <c r="U44" s="4"/>
+      <c r="V44" s="4"/>
+      <c r="W44" s="4"/>
+    </row>
+    <row r="45" ht="21.85" customHeight="1">
+      <c r="A45" s="21"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="25"/>
+      <c r="J45" s="22"/>
+      <c r="K45" s="25"/>
+      <c r="L45" s="22"/>
+      <c r="M45" s="26"/>
+      <c r="N45" s="27"/>
+      <c r="O45" s="28"/>
+      <c r="P45" s="29"/>
+      <c r="Q45" s="30"/>
+      <c r="R45" s="4"/>
+      <c r="S45" s="4"/>
+      <c r="T45" s="4"/>
+      <c r="U45" s="4"/>
+      <c r="V45" s="4"/>
+      <c r="W45" s="4"/>
+    </row>
+    <row r="46" ht="21.85" customHeight="1">
+      <c r="A46" s="21"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="22"/>
+      <c r="I46" s="25"/>
+      <c r="J46" s="22"/>
+      <c r="K46" s="25"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="26"/>
+      <c r="N46" s="27"/>
+      <c r="O46" s="28"/>
+      <c r="P46" s="29"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="4"/>
+      <c r="S46" s="4"/>
+      <c r="T46" s="4"/>
+      <c r="U46" s="4"/>
+      <c r="V46" s="4"/>
+      <c r="W46" s="4"/>
+    </row>
+    <row r="47" ht="21.85" customHeight="1">
+      <c r="A47" s="21"/>
+      <c r="B47" s="22"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="22"/>
+      <c r="I47" s="25"/>
+      <c r="J47" s="22"/>
+      <c r="K47" s="25"/>
+      <c r="L47" s="22"/>
+      <c r="M47" s="26"/>
+      <c r="N47" s="27"/>
+      <c r="O47" s="28"/>
+      <c r="P47" s="29"/>
+      <c r="Q47" s="30"/>
+      <c r="R47" s="4"/>
+      <c r="S47" s="4"/>
+      <c r="T47" s="4"/>
+      <c r="U47" s="4"/>
+      <c r="V47" s="4"/>
+      <c r="W47" s="4"/>
+    </row>
+    <row r="48" ht="21.85" customHeight="1">
+      <c r="A48" s="21"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="23"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="22"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="25"/>
+      <c r="J48" s="22"/>
+      <c r="K48" s="25"/>
+      <c r="L48" s="22"/>
+      <c r="M48" s="26"/>
+      <c r="N48" s="27"/>
+      <c r="O48" s="28"/>
+      <c r="P48" s="29"/>
+      <c r="Q48" s="30"/>
+      <c r="R48" s="4"/>
+      <c r="S48" s="4"/>
+      <c r="T48" s="4"/>
+      <c r="U48" s="4"/>
+      <c r="V48" s="4"/>
+      <c r="W48" s="4"/>
+    </row>
+    <row r="49" ht="21.85" customHeight="1">
+      <c r="A49" s="21"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="23"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="25"/>
+      <c r="J49" s="22"/>
+      <c r="K49" s="25"/>
+      <c r="L49" s="22"/>
+      <c r="M49" s="26"/>
+      <c r="N49" s="27"/>
+      <c r="O49" s="28"/>
+      <c r="P49" s="29"/>
+      <c r="Q49" s="30"/>
+      <c r="R49" s="4"/>
+      <c r="S49" s="4"/>
+      <c r="T49" s="4"/>
+      <c r="U49" s="4"/>
+      <c r="V49" s="4"/>
+      <c r="W49" s="4"/>
+    </row>
+    <row r="50" ht="21.85" customHeight="1">
+      <c r="A50" s="31"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="22"/>
+      <c r="H50" s="22"/>
+      <c r="I50" s="25"/>
+      <c r="J50" s="22"/>
+      <c r="K50" s="25"/>
+      <c r="L50" s="22"/>
+      <c r="M50" s="26"/>
+      <c r="N50" s="27"/>
+      <c r="O50" s="28"/>
+      <c r="P50" s="29"/>
+      <c r="Q50" s="30"/>
+      <c r="R50" s="4"/>
+      <c r="S50" s="4"/>
+      <c r="T50" s="4"/>
+      <c r="U50" s="4"/>
+      <c r="V50" s="4"/>
+      <c r="W50" s="4"/>
+    </row>
+    <row r="51" ht="21.85" customHeight="1">
+      <c r="A51" s="32"/>
+      <c r="B51" s="33"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="33"/>
+      <c r="E51" s="33"/>
+      <c r="F51" s="34" cm="1">
+        <f t="array" ref="F51">SUM(F7:F7)</f>
+        <v>0</v>
+      </c>
+      <c r="G51" s="35" cm="1">
+        <f t="array" ref="G51">SUM(G7:G7)</f>
+        <v>0</v>
+      </c>
+      <c r="H51" s="33"/>
+      <c r="I51" s="35" cm="1">
+        <f t="array" ref="I51">SUM(I7:I7)</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="36" cm="1">
+        <f t="array" ref="J51">SUM(J7:J7)</f>
+        <v>0</v>
+      </c>
+      <c r="K51" s="35" cm="1">
+        <f t="array" ref="K51">SUM(K7:K7)</f>
+        <v>0</v>
+      </c>
+      <c r="L51" s="34" cm="1">
+        <f t="array" ref="L51">SUM(L7:L7)</f>
+        <v>0</v>
+      </c>
+      <c r="M51" s="37" cm="1">
+        <f t="array" ref="M51">SUM(M7:M7)</f>
+        <v>0</v>
+      </c>
+      <c r="N51" s="38" cm="1">
+        <f t="array" ref="N51">SUM(G51+I51+K51+M51)</f>
+        <v>0</v>
+      </c>
+      <c r="O51" s="33"/>
+      <c r="P51" s="33"/>
+      <c r="Q51" s="19"/>
+      <c r="R51" s="4"/>
+      <c r="S51" s="4"/>
+      <c r="T51" s="4"/>
+      <c r="U51" s="4"/>
+      <c r="V51" s="4"/>
+      <c r="W51" s="4"/>
+    </row>
+    <row r="52" ht="21.85" customHeight="1">
+      <c r="A52" s="39"/>
+      <c r="B52" s="40"/>
+      <c r="C52" s="40"/>
+      <c r="D52" t="s" s="41">
+        <v>19</v>
+      </c>
+      <c r="E52" s="42"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="40"/>
+      <c r="I52" s="40"/>
+      <c r="J52" s="40"/>
+      <c r="K52" s="40"/>
+      <c r="L52" s="43"/>
+      <c r="M52" s="44"/>
+      <c r="N52" s="40"/>
+      <c r="O52" s="40"/>
+      <c r="P52" s="40"/>
+      <c r="Q52" s="4"/>
+      <c r="R52" s="4"/>
+      <c r="S52" s="4"/>
+      <c r="T52" s="4"/>
+      <c r="U52" s="4"/>
+      <c r="V52" s="4"/>
+      <c r="W52" s="4"/>
+    </row>
+    <row r="53" ht="21.85" customHeight="1">
+      <c r="A53" s="32"/>
+      <c r="B53" s="45"/>
+      <c r="C53" s="22"/>
+      <c r="D53" t="s" s="46">
+        <v>20</v>
+      </c>
+      <c r="E53" s="47"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="22"/>
+      <c r="I53" s="25"/>
+      <c r="J53" s="22"/>
+      <c r="K53" s="25"/>
+      <c r="L53" s="22"/>
+      <c r="M53" s="26"/>
+      <c r="N53" s="27"/>
+      <c r="O53" t="s" s="23">
+        <v>21</v>
+      </c>
+      <c r="P53" s="48" cm="1">
+        <f t="array" ref="P53">SUM(F51,J51,L51)</f>
+        <v>0</v>
+      </c>
+      <c r="Q53" s="19"/>
+      <c r="R53" s="4"/>
+      <c r="S53" s="4"/>
+      <c r="T53" s="4"/>
+      <c r="U53" s="4"/>
+      <c r="V53" s="4"/>
+      <c r="W53" s="4"/>
+    </row>
+    <row r="54" ht="21.85" customHeight="1">
+      <c r="A54" s="32"/>
+      <c r="B54" s="45"/>
+      <c r="C54" s="22"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="47"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="22"/>
+      <c r="H54" s="22"/>
+      <c r="I54" s="25"/>
+      <c r="J54" s="22"/>
+      <c r="K54" s="25"/>
+      <c r="L54" s="22"/>
+      <c r="M54" s="26"/>
+      <c r="N54" s="27"/>
+      <c r="O54" t="s" s="23">
+        <v>22</v>
+      </c>
+      <c r="P54" s="48" cm="1">
+        <f t="array" ref="P54">SUM(G51+K51+M51)</f>
+        <v>0</v>
+      </c>
+      <c r="Q54" s="19"/>
+      <c r="R54" s="4"/>
+      <c r="S54" s="4"/>
+      <c r="T54" s="4"/>
+      <c r="U54" s="4"/>
+      <c r="V54" s="4"/>
+      <c r="W54" s="4"/>
+    </row>
+    <row r="55" ht="148.75" customHeight="1">
+      <c r="A55" t="s" s="49">
+        <v>23</v>
+      </c>
+      <c r="B55" s="50"/>
+      <c r="C55" s="50"/>
+      <c r="D55" t="s" s="51">
+        <v>24</v>
+      </c>
+      <c r="E55" t="s" s="52">
+        <v>25</v>
+      </c>
+      <c r="F55" s="53"/>
+      <c r="G55" s="53"/>
+      <c r="H55" s="54"/>
+      <c r="I55" s="54"/>
+      <c r="J55" t="s" s="55">
+        <v>26</v>
+      </c>
+      <c r="K55" s="54"/>
+      <c r="L55" s="54"/>
+      <c r="M55" s="56"/>
+      <c r="N55" s="54"/>
+      <c r="O55" s="54"/>
+      <c r="P55" s="54"/>
+      <c r="Q55" s="4"/>
+      <c r="R55" s="4"/>
+      <c r="S55" s="4"/>
+      <c r="T55" s="4"/>
+      <c r="U55" s="4"/>
+      <c r="V55" s="4"/>
+      <c r="W55" s="4"/>
+    </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="O5:P5"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="E55:G55"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
@@ -2104,7 +3182,7 @@
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="J5:K5"/>
   </mergeCells>
-  <conditionalFormatting sqref="M7:M8 M10:M11">
+  <conditionalFormatting sqref="M7:M51 M53:M54">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan" stopIfTrue="1">
       <formula>0</formula>
     </cfRule>

--- a/template.xlsx
+++ b/template.xlsx
@@ -122,7 +122,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color indexed="11"/>
+        <color indexed="10"/>
         <rFont val="新細明體"/>
       </rPr>
       <t xml:space="preserve">
@@ -141,7 +141,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color indexed="11"/>
+        <color indexed="10"/>
         <rFont val="新細明體"/>
       </rPr>
       <t xml:space="preserve">
@@ -206,7 +206,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <color indexed="11"/>
+      <color indexed="10"/>
       <name val="新細明體"/>
     </font>
     <font>
@@ -230,18 +230,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="13"/>
+        <fgColor indexed="12"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="14"/>
+        <fgColor indexed="13"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -251,55 +251,10 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="8"/>
       </left>
-      <right style="thin">
+      <right>
         <color indexed="8"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
       </right>
       <top style="thin">
         <color indexed="8"/>
@@ -310,8 +265,23 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="10"/>
+      <left>
+        <color indexed="8"/>
+      </left>
+      <right>
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left>
+        <color indexed="8"/>
       </left>
       <right style="thin">
         <color indexed="8"/>
@@ -344,13 +314,13 @@
         <color indexed="8"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </top>
-      <bottom style="thin">
-        <color indexed="10"/>
+      <bottom>
+        <color indexed="8"/>
       </bottom>
       <diagonal/>
     </border>
@@ -361,52 +331,7 @@
       <right style="thin">
         <color indexed="8"/>
       </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
+      <top>
         <color indexed="8"/>
       </top>
       <bottom style="thin">
@@ -414,43 +339,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -460,166 +355,136 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="59" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="59" fontId="3" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="59" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="59" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="59" fontId="0" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="60" fontId="5" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="61" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="62" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="60" fontId="5" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="61" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="61" fontId="4" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="62" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="62" fontId="4" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="20" fontId="4" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="60" fontId="5" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="61" fontId="4" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="61" fontId="0" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="62" fontId="4" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="61" fontId="0" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="62" fontId="0" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="59" fontId="0" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="4" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="59" fontId="0" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="59" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -646,7 +511,6 @@
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
       <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffaaaaaa"/>
       <rgbColor rgb="ff0000d4"/>
       <rgbColor rgb="ffff0000"/>
       <rgbColor rgb="ffccffcc"/>
@@ -1709,1462 +1573,1465 @@
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="7"/>
     </row>
     <row r="2" ht="30.6" customHeight="1">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
     </row>
     <row r="3" ht="21.85" customHeight="1">
-      <c r="A3" t="s" s="7">
+      <c r="A3" t="s" s="10">
         <v>1</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="5"/>
-      <c r="D3" t="s" s="7">
+      <c r="B3" s="11"/>
+      <c r="C3" s="6"/>
+      <c r="D3" t="s" s="10">
         <v>2</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" t="s" s="9">
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" t="s" s="12">
         <v>3</v>
       </c>
-      <c r="K3" s="10"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
     </row>
     <row r="4" ht="21.85" customHeight="1">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
     </row>
     <row r="5" ht="21.85" customHeight="1">
-      <c r="A5" t="s" s="14">
+      <c r="A5" t="s" s="15">
         <v>4</v>
       </c>
-      <c r="B5" t="s" s="14">
+      <c r="B5" t="s" s="15">
         <v>5</v>
       </c>
-      <c r="C5" t="s" s="14">
+      <c r="C5" t="s" s="15">
         <v>6</v>
       </c>
-      <c r="D5" t="s" s="14">
+      <c r="D5" t="s" s="15">
         <v>7</v>
       </c>
-      <c r="E5" t="s" s="14">
+      <c r="E5" t="s" s="15">
         <v>8</v>
       </c>
-      <c r="F5" t="s" s="15">
+      <c r="F5" t="s" s="16">
         <v>9</v>
       </c>
-      <c r="G5" s="16"/>
-      <c r="H5" t="s" s="15">
+      <c r="G5" s="17"/>
+      <c r="H5" t="s" s="16">
         <v>10</v>
       </c>
-      <c r="I5" s="16"/>
-      <c r="J5" t="s" s="15">
+      <c r="I5" s="17"/>
+      <c r="J5" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K5" s="16"/>
-      <c r="L5" t="s" s="15">
+      <c r="K5" s="17"/>
+      <c r="L5" t="s" s="16">
         <v>12</v>
       </c>
-      <c r="M5" s="16"/>
-      <c r="N5" t="s" s="17">
+      <c r="M5" s="17"/>
+      <c r="N5" t="s" s="18">
         <v>13</v>
       </c>
-      <c r="O5" t="s" s="17">
+      <c r="O5" t="s" s="16">
         <v>14</v>
       </c>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
     </row>
     <row r="6" ht="21.85" customHeight="1">
-      <c r="A6" s="20"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" t="s" s="17">
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" t="s" s="18">
         <v>15</v>
       </c>
-      <c r="G6" t="s" s="17">
+      <c r="G6" t="s" s="18">
         <v>16</v>
       </c>
-      <c r="H6" t="s" s="17">
+      <c r="H6" t="s" s="18">
         <v>15</v>
       </c>
-      <c r="I6" t="s" s="17">
+      <c r="I6" t="s" s="18">
         <v>16</v>
       </c>
-      <c r="J6" t="s" s="17">
+      <c r="J6" t="s" s="18">
         <v>15</v>
       </c>
-      <c r="K6" t="s" s="17">
+      <c r="K6" t="s" s="18">
         <v>16</v>
       </c>
-      <c r="L6" t="s" s="17">
+      <c r="L6" t="s" s="18">
         <v>15</v>
       </c>
-      <c r="M6" t="s" s="17">
+      <c r="M6" t="s" s="18">
         <v>16</v>
       </c>
-      <c r="N6" t="s" s="17">
+      <c r="N6" t="s" s="18">
         <v>16</v>
       </c>
-      <c r="O6" t="s" s="17">
+      <c r="O6" t="s" s="18">
         <v>17</v>
       </c>
-      <c r="P6" t="s" s="17">
+      <c r="P6" t="s" s="18">
         <v>18</v>
       </c>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
-      <c r="W6" s="4"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
     </row>
     <row r="7" ht="21.85" customHeight="1">
-      <c r="A7" s="21"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="27"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="30"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
-      <c r="W7" s="4"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="26"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
     </row>
     <row r="8" ht="21.85" customHeight="1">
-      <c r="A8" s="21"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="27"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="30"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
     </row>
     <row r="9" ht="21.85" customHeight="1">
-      <c r="A9" s="21"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="28"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="30"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
     </row>
     <row r="10" ht="21.85" customHeight="1">
-      <c r="A10" s="21"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="27"/>
-      <c r="O10" s="28"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="30"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
     </row>
     <row r="11" ht="21.85" customHeight="1">
-      <c r="A11" s="21"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="28"/>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="30"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="26"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
     </row>
     <row r="12" ht="21.85" customHeight="1">
-      <c r="A12" s="21"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="27"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="30"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
-      <c r="W12" s="4"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="18"/>
+      <c r="Q12" s="26"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
     </row>
     <row r="13" ht="21.85" customHeight="1">
-      <c r="A13" s="21"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="25"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="27"/>
-      <c r="O13" s="28"/>
-      <c r="P13" s="29"/>
-      <c r="Q13" s="30"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="26"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
     </row>
     <row r="14" ht="21.85" customHeight="1">
-      <c r="A14" s="21"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="25"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="27"/>
-      <c r="O14" s="28"/>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="30"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
-      <c r="W14" s="4"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
     </row>
     <row r="15" ht="21.85" customHeight="1">
-      <c r="A15" s="21"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="27"/>
-      <c r="O15" s="28"/>
-      <c r="P15" s="29"/>
-      <c r="Q15" s="30"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="4"/>
-      <c r="W15" s="4"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="26"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
     </row>
     <row r="16" ht="21.85" customHeight="1">
-      <c r="A16" s="21"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="26"/>
-      <c r="N16" s="27"/>
-      <c r="O16" s="28"/>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="30"/>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
-      <c r="W16" s="4"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="18"/>
+      <c r="Q16" s="26"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
     </row>
     <row r="17" ht="21.85" customHeight="1">
-      <c r="A17" s="21"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="26"/>
-      <c r="N17" s="27"/>
-      <c r="O17" s="28"/>
-      <c r="P17" s="29"/>
-      <c r="Q17" s="30"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="4"/>
-      <c r="W17" s="4"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="18"/>
+      <c r="Q17" s="26"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
     </row>
     <row r="18" ht="21.85" customHeight="1">
-      <c r="A18" s="21"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="25"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="26"/>
-      <c r="N18" s="27"/>
-      <c r="O18" s="28"/>
-      <c r="P18" s="29"/>
-      <c r="Q18" s="30"/>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
-      <c r="V18" s="4"/>
-      <c r="W18" s="4"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="26"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7"/>
     </row>
     <row r="19" ht="21.85" customHeight="1">
-      <c r="A19" s="21"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="26"/>
-      <c r="N19" s="27"/>
-      <c r="O19" s="28"/>
-      <c r="P19" s="29"/>
-      <c r="Q19" s="30"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="4"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="25"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="26"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
     </row>
     <row r="20" ht="21.85" customHeight="1">
-      <c r="A20" s="21"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="26"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="4"/>
-      <c r="S20" s="4"/>
-      <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
-      <c r="V20" s="4"/>
-      <c r="W20" s="4"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="24"/>
+      <c r="O20" s="25"/>
+      <c r="P20" s="18"/>
+      <c r="Q20" s="26"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="7"/>
+      <c r="W20" s="7"/>
     </row>
     <row r="21" ht="21.85" customHeight="1">
-      <c r="A21" s="21"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="25"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="26"/>
-      <c r="N21" s="27"/>
-      <c r="O21" s="28"/>
-      <c r="P21" s="29"/>
-      <c r="Q21" s="30"/>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4"/>
-      <c r="T21" s="4"/>
-      <c r="U21" s="4"/>
-      <c r="V21" s="4"/>
-      <c r="W21" s="4"/>
+      <c r="A21" s="20"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="24"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="26"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="7"/>
+      <c r="U21" s="7"/>
+      <c r="V21" s="7"/>
+      <c r="W21" s="7"/>
     </row>
     <row r="22" ht="21.85" customHeight="1">
-      <c r="A22" s="21"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="26"/>
-      <c r="N22" s="27"/>
-      <c r="O22" s="28"/>
-      <c r="P22" s="29"/>
-      <c r="Q22" s="30"/>
-      <c r="R22" s="4"/>
-      <c r="S22" s="4"/>
-      <c r="T22" s="4"/>
-      <c r="U22" s="4"/>
-      <c r="V22" s="4"/>
-      <c r="W22" s="4"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="25"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="7"/>
+      <c r="W22" s="7"/>
     </row>
     <row r="23" ht="21.85" customHeight="1">
-      <c r="A23" s="21"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="4"/>
-      <c r="S23" s="4"/>
-      <c r="T23" s="4"/>
-      <c r="U23" s="4"/>
-      <c r="V23" s="4"/>
-      <c r="W23" s="4"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="25"/>
+      <c r="P23" s="18"/>
+      <c r="Q23" s="26"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7"/>
     </row>
     <row r="24" ht="21.85" customHeight="1">
-      <c r="A24" s="21"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="22"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="27"/>
-      <c r="O24" s="28"/>
-      <c r="P24" s="29"/>
-      <c r="Q24" s="30"/>
-      <c r="R24" s="4"/>
-      <c r="S24" s="4"/>
-      <c r="T24" s="4"/>
-      <c r="U24" s="4"/>
-      <c r="V24" s="4"/>
-      <c r="W24" s="4"/>
+      <c r="A24" s="20"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="24"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="18"/>
+      <c r="Q24" s="26"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="W24" s="7"/>
     </row>
     <row r="25" ht="21.85" customHeight="1">
-      <c r="A25" s="21"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="25"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="26"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="28"/>
-      <c r="P25" s="29"/>
-      <c r="Q25" s="30"/>
-      <c r="R25" s="4"/>
-      <c r="S25" s="4"/>
-      <c r="T25" s="4"/>
-      <c r="U25" s="4"/>
-      <c r="V25" s="4"/>
-      <c r="W25" s="4"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="26"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="7"/>
     </row>
     <row r="26" ht="21.85" customHeight="1">
-      <c r="A26" s="21"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="25"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="25"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="26"/>
-      <c r="N26" s="27"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="30"/>
-      <c r="R26" s="4"/>
-      <c r="S26" s="4"/>
-      <c r="T26" s="4"/>
-      <c r="U26" s="4"/>
-      <c r="V26" s="4"/>
-      <c r="W26" s="4"/>
+      <c r="A26" s="20"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="23"/>
+      <c r="N26" s="24"/>
+      <c r="O26" s="25"/>
+      <c r="P26" s="18"/>
+      <c r="Q26" s="26"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
+      <c r="U26" s="7"/>
+      <c r="V26" s="7"/>
+      <c r="W26" s="7"/>
     </row>
     <row r="27" ht="21.85" customHeight="1">
-      <c r="A27" s="21"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="25"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="25"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="27"/>
-      <c r="O27" s="28"/>
-      <c r="P27" s="29"/>
-      <c r="Q27" s="30"/>
-      <c r="R27" s="4"/>
-      <c r="S27" s="4"/>
-      <c r="T27" s="4"/>
-      <c r="U27" s="4"/>
-      <c r="V27" s="4"/>
-      <c r="W27" s="4"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="24"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="7"/>
+      <c r="W27" s="7"/>
     </row>
     <row r="28" ht="21.85" customHeight="1">
-      <c r="A28" s="21"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="25"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="27"/>
-      <c r="O28" s="28"/>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="30"/>
-      <c r="R28" s="4"/>
-      <c r="S28" s="4"/>
-      <c r="T28" s="4"/>
-      <c r="U28" s="4"/>
-      <c r="V28" s="4"/>
-      <c r="W28" s="4"/>
+      <c r="A28" s="20"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="24"/>
+      <c r="O28" s="25"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="26"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
+      <c r="U28" s="7"/>
+      <c r="V28" s="7"/>
+      <c r="W28" s="7"/>
     </row>
     <row r="29" ht="21.85" customHeight="1">
-      <c r="A29" s="21"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="25"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="25"/>
-      <c r="L29" s="22"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="4"/>
-      <c r="S29" s="4"/>
-      <c r="T29" s="4"/>
-      <c r="U29" s="4"/>
-      <c r="V29" s="4"/>
-      <c r="W29" s="4"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="23"/>
+      <c r="N29" s="24"/>
+      <c r="O29" s="25"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="26"/>
+      <c r="R29" s="7"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7"/>
+      <c r="U29" s="7"/>
+      <c r="V29" s="7"/>
+      <c r="W29" s="7"/>
     </row>
     <row r="30" ht="21.85" customHeight="1">
-      <c r="A30" s="21"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="25"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="25"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="26"/>
-      <c r="N30" s="27"/>
-      <c r="O30" s="28"/>
-      <c r="P30" s="29"/>
-      <c r="Q30" s="30"/>
-      <c r="R30" s="4"/>
-      <c r="S30" s="4"/>
-      <c r="T30" s="4"/>
-      <c r="U30" s="4"/>
-      <c r="V30" s="4"/>
-      <c r="W30" s="4"/>
+      <c r="A30" s="20"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="23"/>
+      <c r="N30" s="24"/>
+      <c r="O30" s="25"/>
+      <c r="P30" s="18"/>
+      <c r="Q30" s="26"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="7"/>
+      <c r="U30" s="7"/>
+      <c r="V30" s="7"/>
+      <c r="W30" s="7"/>
     </row>
     <row r="31" ht="21.85" customHeight="1">
-      <c r="A31" s="21"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="25"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="25"/>
-      <c r="L31" s="22"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="27"/>
-      <c r="O31" s="28"/>
-      <c r="P31" s="29"/>
-      <c r="Q31" s="30"/>
-      <c r="R31" s="4"/>
-      <c r="S31" s="4"/>
-      <c r="T31" s="4"/>
-      <c r="U31" s="4"/>
-      <c r="V31" s="4"/>
-      <c r="W31" s="4"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="24"/>
+      <c r="O31" s="25"/>
+      <c r="P31" s="18"/>
+      <c r="Q31" s="26"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7"/>
     </row>
     <row r="32" ht="21.85" customHeight="1">
-      <c r="A32" s="21"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="25"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="25"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="27"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="4"/>
-      <c r="S32" s="4"/>
-      <c r="T32" s="4"/>
-      <c r="U32" s="4"/>
-      <c r="V32" s="4"/>
-      <c r="W32" s="4"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="23"/>
+      <c r="N32" s="24"/>
+      <c r="O32" s="25"/>
+      <c r="P32" s="18"/>
+      <c r="Q32" s="26"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7"/>
+      <c r="U32" s="7"/>
+      <c r="V32" s="7"/>
+      <c r="W32" s="7"/>
     </row>
     <row r="33" ht="21.85" customHeight="1">
-      <c r="A33" s="21"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="25"/>
-      <c r="J33" s="22"/>
-      <c r="K33" s="25"/>
-      <c r="L33" s="22"/>
-      <c r="M33" s="26"/>
-      <c r="N33" s="27"/>
-      <c r="O33" s="28"/>
-      <c r="P33" s="29"/>
-      <c r="Q33" s="30"/>
-      <c r="R33" s="4"/>
-      <c r="S33" s="4"/>
-      <c r="T33" s="4"/>
-      <c r="U33" s="4"/>
-      <c r="V33" s="4"/>
-      <c r="W33" s="4"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="23"/>
+      <c r="N33" s="24"/>
+      <c r="O33" s="25"/>
+      <c r="P33" s="18"/>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="7"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
+      <c r="U33" s="7"/>
+      <c r="V33" s="7"/>
+      <c r="W33" s="7"/>
     </row>
     <row r="34" ht="21.85" customHeight="1">
-      <c r="A34" s="21"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="22"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="27"/>
-      <c r="O34" s="28"/>
-      <c r="P34" s="29"/>
-      <c r="Q34" s="30"/>
-      <c r="R34" s="4"/>
-      <c r="S34" s="4"/>
-      <c r="T34" s="4"/>
-      <c r="U34" s="4"/>
-      <c r="V34" s="4"/>
-      <c r="W34" s="4"/>
+      <c r="A34" s="20"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="23"/>
+      <c r="N34" s="24"/>
+      <c r="O34" s="25"/>
+      <c r="P34" s="18"/>
+      <c r="Q34" s="26"/>
+      <c r="R34" s="7"/>
+      <c r="S34" s="7"/>
+      <c r="T34" s="7"/>
+      <c r="U34" s="7"/>
+      <c r="V34" s="7"/>
+      <c r="W34" s="7"/>
     </row>
     <row r="35" ht="21.85" customHeight="1">
-      <c r="A35" s="21"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="22"/>
-      <c r="K35" s="25"/>
-      <c r="L35" s="22"/>
-      <c r="M35" s="26"/>
-      <c r="N35" s="27"/>
-      <c r="O35" s="28"/>
-      <c r="P35" s="29"/>
-      <c r="Q35" s="30"/>
-      <c r="R35" s="4"/>
-      <c r="S35" s="4"/>
-      <c r="T35" s="4"/>
-      <c r="U35" s="4"/>
-      <c r="V35" s="4"/>
-      <c r="W35" s="4"/>
+      <c r="A35" s="20"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="23"/>
+      <c r="N35" s="24"/>
+      <c r="O35" s="25"/>
+      <c r="P35" s="18"/>
+      <c r="Q35" s="26"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+      <c r="U35" s="7"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="7"/>
     </row>
     <row r="36" ht="21.85" customHeight="1">
-      <c r="A36" s="21"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="25"/>
-      <c r="J36" s="22"/>
-      <c r="K36" s="25"/>
-      <c r="L36" s="22"/>
-      <c r="M36" s="26"/>
-      <c r="N36" s="27"/>
-      <c r="O36" s="28"/>
-      <c r="P36" s="29"/>
-      <c r="Q36" s="30"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
-      <c r="V36" s="4"/>
-      <c r="W36" s="4"/>
+      <c r="A36" s="20"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="23"/>
+      <c r="N36" s="24"/>
+      <c r="O36" s="25"/>
+      <c r="P36" s="18"/>
+      <c r="Q36" s="26"/>
+      <c r="R36" s="7"/>
+      <c r="S36" s="7"/>
+      <c r="T36" s="7"/>
+      <c r="U36" s="7"/>
+      <c r="V36" s="7"/>
+      <c r="W36" s="7"/>
     </row>
     <row r="37" ht="21.85" customHeight="1">
-      <c r="A37" s="21"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="25"/>
-      <c r="J37" s="22"/>
-      <c r="K37" s="25"/>
-      <c r="L37" s="22"/>
-      <c r="M37" s="26"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="30"/>
-      <c r="R37" s="4"/>
-      <c r="S37" s="4"/>
-      <c r="T37" s="4"/>
-      <c r="U37" s="4"/>
-      <c r="V37" s="4"/>
-      <c r="W37" s="4"/>
+      <c r="A37" s="20"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="23"/>
+      <c r="N37" s="24"/>
+      <c r="O37" s="25"/>
+      <c r="P37" s="18"/>
+      <c r="Q37" s="26"/>
+      <c r="R37" s="7"/>
+      <c r="S37" s="7"/>
+      <c r="T37" s="7"/>
+      <c r="U37" s="7"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7"/>
     </row>
     <row r="38" ht="21.85" customHeight="1">
-      <c r="A38" s="21"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="25"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="25"/>
-      <c r="L38" s="22"/>
-      <c r="M38" s="26"/>
-      <c r="N38" s="27"/>
-      <c r="O38" s="28"/>
-      <c r="P38" s="29"/>
-      <c r="Q38" s="30"/>
-      <c r="R38" s="4"/>
-      <c r="S38" s="4"/>
-      <c r="T38" s="4"/>
-      <c r="U38" s="4"/>
-      <c r="V38" s="4"/>
-      <c r="W38" s="4"/>
+      <c r="A38" s="20"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="23"/>
+      <c r="N38" s="24"/>
+      <c r="O38" s="25"/>
+      <c r="P38" s="18"/>
+      <c r="Q38" s="26"/>
+      <c r="R38" s="7"/>
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
+      <c r="U38" s="7"/>
+      <c r="V38" s="7"/>
+      <c r="W38" s="7"/>
     </row>
     <row r="39" ht="21.85" customHeight="1">
-      <c r="A39" s="21"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="25"/>
-      <c r="J39" s="22"/>
-      <c r="K39" s="25"/>
-      <c r="L39" s="22"/>
-      <c r="M39" s="26"/>
-      <c r="N39" s="27"/>
-      <c r="O39" s="28"/>
-      <c r="P39" s="29"/>
-      <c r="Q39" s="30"/>
-      <c r="R39" s="4"/>
-      <c r="S39" s="4"/>
-      <c r="T39" s="4"/>
-      <c r="U39" s="4"/>
-      <c r="V39" s="4"/>
-      <c r="W39" s="4"/>
+      <c r="A39" s="20"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="23"/>
+      <c r="N39" s="24"/>
+      <c r="O39" s="25"/>
+      <c r="P39" s="18"/>
+      <c r="Q39" s="26"/>
+      <c r="R39" s="7"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
+      <c r="U39" s="7"/>
+      <c r="V39" s="7"/>
+      <c r="W39" s="7"/>
     </row>
     <row r="40" ht="21.85" customHeight="1">
-      <c r="A40" s="21"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="22"/>
-      <c r="I40" s="25"/>
-      <c r="J40" s="22"/>
-      <c r="K40" s="25"/>
-      <c r="L40" s="22"/>
-      <c r="M40" s="26"/>
-      <c r="N40" s="27"/>
-      <c r="O40" s="28"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="30"/>
-      <c r="R40" s="4"/>
-      <c r="S40" s="4"/>
-      <c r="T40" s="4"/>
-      <c r="U40" s="4"/>
-      <c r="V40" s="4"/>
-      <c r="W40" s="4"/>
+      <c r="A40" s="20"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="22"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="23"/>
+      <c r="N40" s="24"/>
+      <c r="O40" s="25"/>
+      <c r="P40" s="18"/>
+      <c r="Q40" s="26"/>
+      <c r="R40" s="7"/>
+      <c r="S40" s="7"/>
+      <c r="T40" s="7"/>
+      <c r="U40" s="7"/>
+      <c r="V40" s="7"/>
+      <c r="W40" s="7"/>
     </row>
     <row r="41" ht="21.85" customHeight="1">
-      <c r="A41" s="21"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="25"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="25"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="26"/>
-      <c r="N41" s="27"/>
-      <c r="O41" s="28"/>
-      <c r="P41" s="29"/>
-      <c r="Q41" s="30"/>
-      <c r="R41" s="4"/>
-      <c r="S41" s="4"/>
-      <c r="T41" s="4"/>
-      <c r="U41" s="4"/>
-      <c r="V41" s="4"/>
-      <c r="W41" s="4"/>
+      <c r="A41" s="20"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="23"/>
+      <c r="N41" s="24"/>
+      <c r="O41" s="25"/>
+      <c r="P41" s="18"/>
+      <c r="Q41" s="26"/>
+      <c r="R41" s="7"/>
+      <c r="S41" s="7"/>
+      <c r="T41" s="7"/>
+      <c r="U41" s="7"/>
+      <c r="V41" s="7"/>
+      <c r="W41" s="7"/>
     </row>
     <row r="42" ht="21.85" customHeight="1">
-      <c r="A42" s="21"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="22"/>
-      <c r="I42" s="25"/>
-      <c r="J42" s="22"/>
-      <c r="K42" s="25"/>
-      <c r="L42" s="22"/>
-      <c r="M42" s="26"/>
-      <c r="N42" s="27"/>
-      <c r="O42" s="28"/>
-      <c r="P42" s="29"/>
-      <c r="Q42" s="30"/>
-      <c r="R42" s="4"/>
-      <c r="S42" s="4"/>
-      <c r="T42" s="4"/>
-      <c r="U42" s="4"/>
-      <c r="V42" s="4"/>
-      <c r="W42" s="4"/>
+      <c r="A42" s="20"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="23"/>
+      <c r="N42" s="24"/>
+      <c r="O42" s="25"/>
+      <c r="P42" s="18"/>
+      <c r="Q42" s="26"/>
+      <c r="R42" s="7"/>
+      <c r="S42" s="7"/>
+      <c r="T42" s="7"/>
+      <c r="U42" s="7"/>
+      <c r="V42" s="7"/>
+      <c r="W42" s="7"/>
     </row>
     <row r="43" ht="21.85" customHeight="1">
-      <c r="A43" s="21"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="25"/>
-      <c r="J43" s="22"/>
-      <c r="K43" s="25"/>
-      <c r="L43" s="22"/>
-      <c r="M43" s="26"/>
-      <c r="N43" s="27"/>
-      <c r="O43" s="28"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="30"/>
-      <c r="R43" s="4"/>
-      <c r="S43" s="4"/>
-      <c r="T43" s="4"/>
-      <c r="U43" s="4"/>
-      <c r="V43" s="4"/>
-      <c r="W43" s="4"/>
+      <c r="A43" s="20"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="22"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="23"/>
+      <c r="N43" s="24"/>
+      <c r="O43" s="25"/>
+      <c r="P43" s="18"/>
+      <c r="Q43" s="26"/>
+      <c r="R43" s="7"/>
+      <c r="S43" s="7"/>
+      <c r="T43" s="7"/>
+      <c r="U43" s="7"/>
+      <c r="V43" s="7"/>
+      <c r="W43" s="7"/>
     </row>
     <row r="44" ht="21.85" customHeight="1">
-      <c r="A44" s="21"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="23"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="22"/>
-      <c r="H44" s="22"/>
-      <c r="I44" s="25"/>
-      <c r="J44" s="22"/>
-      <c r="K44" s="25"/>
-      <c r="L44" s="22"/>
-      <c r="M44" s="26"/>
-      <c r="N44" s="27"/>
-      <c r="O44" s="28"/>
-      <c r="P44" s="29"/>
-      <c r="Q44" s="30"/>
-      <c r="R44" s="4"/>
-      <c r="S44" s="4"/>
-      <c r="T44" s="4"/>
-      <c r="U44" s="4"/>
-      <c r="V44" s="4"/>
-      <c r="W44" s="4"/>
+      <c r="A44" s="20"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="22"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="23"/>
+      <c r="N44" s="24"/>
+      <c r="O44" s="25"/>
+      <c r="P44" s="18"/>
+      <c r="Q44" s="26"/>
+      <c r="R44" s="7"/>
+      <c r="S44" s="7"/>
+      <c r="T44" s="7"/>
+      <c r="U44" s="7"/>
+      <c r="V44" s="7"/>
+      <c r="W44" s="7"/>
     </row>
     <row r="45" ht="21.85" customHeight="1">
-      <c r="A45" s="21"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="23"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="22"/>
-      <c r="G45" s="22"/>
-      <c r="H45" s="22"/>
-      <c r="I45" s="25"/>
-      <c r="J45" s="22"/>
-      <c r="K45" s="25"/>
-      <c r="L45" s="22"/>
-      <c r="M45" s="26"/>
-      <c r="N45" s="27"/>
-      <c r="O45" s="28"/>
-      <c r="P45" s="29"/>
-      <c r="Q45" s="30"/>
-      <c r="R45" s="4"/>
-      <c r="S45" s="4"/>
-      <c r="T45" s="4"/>
-      <c r="U45" s="4"/>
-      <c r="V45" s="4"/>
-      <c r="W45" s="4"/>
+      <c r="A45" s="20"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="22"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="22"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="23"/>
+      <c r="N45" s="24"/>
+      <c r="O45" s="25"/>
+      <c r="P45" s="18"/>
+      <c r="Q45" s="26"/>
+      <c r="R45" s="7"/>
+      <c r="S45" s="7"/>
+      <c r="T45" s="7"/>
+      <c r="U45" s="7"/>
+      <c r="V45" s="7"/>
+      <c r="W45" s="7"/>
     </row>
     <row r="46" ht="21.85" customHeight="1">
-      <c r="A46" s="21"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="23"/>
-      <c r="D46" s="24"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="22"/>
-      <c r="H46" s="22"/>
-      <c r="I46" s="25"/>
-      <c r="J46" s="22"/>
-      <c r="K46" s="25"/>
-      <c r="L46" s="22"/>
-      <c r="M46" s="26"/>
-      <c r="N46" s="27"/>
-      <c r="O46" s="28"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="30"/>
-      <c r="R46" s="4"/>
-      <c r="S46" s="4"/>
-      <c r="T46" s="4"/>
-      <c r="U46" s="4"/>
-      <c r="V46" s="4"/>
-      <c r="W46" s="4"/>
+      <c r="A46" s="20"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="22"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="22"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="23"/>
+      <c r="N46" s="24"/>
+      <c r="O46" s="25"/>
+      <c r="P46" s="18"/>
+      <c r="Q46" s="26"/>
+      <c r="R46" s="7"/>
+      <c r="S46" s="7"/>
+      <c r="T46" s="7"/>
+      <c r="U46" s="7"/>
+      <c r="V46" s="7"/>
+      <c r="W46" s="7"/>
     </row>
     <row r="47" ht="21.85" customHeight="1">
-      <c r="A47" s="21"/>
-      <c r="B47" s="22"/>
-      <c r="C47" s="23"/>
-      <c r="D47" s="24"/>
-      <c r="E47" s="23"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="22"/>
-      <c r="I47" s="25"/>
-      <c r="J47" s="22"/>
-      <c r="K47" s="25"/>
-      <c r="L47" s="22"/>
-      <c r="M47" s="26"/>
-      <c r="N47" s="27"/>
-      <c r="O47" s="28"/>
-      <c r="P47" s="29"/>
-      <c r="Q47" s="30"/>
-      <c r="R47" s="4"/>
-      <c r="S47" s="4"/>
-      <c r="T47" s="4"/>
-      <c r="U47" s="4"/>
-      <c r="V47" s="4"/>
-      <c r="W47" s="4"/>
+      <c r="A47" s="20"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="22"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="22"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="23"/>
+      <c r="N47" s="24"/>
+      <c r="O47" s="25"/>
+      <c r="P47" s="18"/>
+      <c r="Q47" s="26"/>
+      <c r="R47" s="7"/>
+      <c r="S47" s="7"/>
+      <c r="T47" s="7"/>
+      <c r="U47" s="7"/>
+      <c r="V47" s="7"/>
+      <c r="W47" s="7"/>
     </row>
     <row r="48" ht="21.85" customHeight="1">
-      <c r="A48" s="21"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="23"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="22"/>
-      <c r="I48" s="25"/>
-      <c r="J48" s="22"/>
-      <c r="K48" s="25"/>
-      <c r="L48" s="22"/>
-      <c r="M48" s="26"/>
-      <c r="N48" s="27"/>
-      <c r="O48" s="28"/>
-      <c r="P48" s="29"/>
-      <c r="Q48" s="30"/>
-      <c r="R48" s="4"/>
-      <c r="S48" s="4"/>
-      <c r="T48" s="4"/>
-      <c r="U48" s="4"/>
-      <c r="V48" s="4"/>
-      <c r="W48" s="4"/>
+      <c r="A48" s="20"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="22"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="22"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="23"/>
+      <c r="N48" s="24"/>
+      <c r="O48" s="25"/>
+      <c r="P48" s="18"/>
+      <c r="Q48" s="26"/>
+      <c r="R48" s="7"/>
+      <c r="S48" s="7"/>
+      <c r="T48" s="7"/>
+      <c r="U48" s="7"/>
+      <c r="V48" s="7"/>
+      <c r="W48" s="7"/>
     </row>
     <row r="49" ht="21.85" customHeight="1">
-      <c r="A49" s="21"/>
-      <c r="B49" s="22"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="24"/>
-      <c r="E49" s="23"/>
-      <c r="F49" s="22"/>
-      <c r="G49" s="22"/>
-      <c r="H49" s="22"/>
-      <c r="I49" s="25"/>
-      <c r="J49" s="22"/>
-      <c r="K49" s="25"/>
-      <c r="L49" s="22"/>
-      <c r="M49" s="26"/>
-      <c r="N49" s="27"/>
-      <c r="O49" s="28"/>
-      <c r="P49" s="29"/>
-      <c r="Q49" s="30"/>
-      <c r="R49" s="4"/>
-      <c r="S49" s="4"/>
-      <c r="T49" s="4"/>
-      <c r="U49" s="4"/>
-      <c r="V49" s="4"/>
-      <c r="W49" s="4"/>
+      <c r="A49" s="20"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="22"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="22"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="23"/>
+      <c r="N49" s="24"/>
+      <c r="O49" s="25"/>
+      <c r="P49" s="18"/>
+      <c r="Q49" s="26"/>
+      <c r="R49" s="7"/>
+      <c r="S49" s="7"/>
+      <c r="T49" s="7"/>
+      <c r="U49" s="7"/>
+      <c r="V49" s="7"/>
+      <c r="W49" s="7"/>
     </row>
     <row r="50" ht="21.85" customHeight="1">
-      <c r="A50" s="31"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="24"/>
-      <c r="E50" s="23"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="22"/>
-      <c r="H50" s="22"/>
-      <c r="I50" s="25"/>
-      <c r="J50" s="22"/>
-      <c r="K50" s="25"/>
-      <c r="L50" s="22"/>
-      <c r="M50" s="26"/>
-      <c r="N50" s="27"/>
-      <c r="O50" s="28"/>
-      <c r="P50" s="29"/>
-      <c r="Q50" s="30"/>
-      <c r="R50" s="4"/>
-      <c r="S50" s="4"/>
-      <c r="T50" s="4"/>
-      <c r="U50" s="4"/>
-      <c r="V50" s="4"/>
-      <c r="W50" s="4"/>
+      <c r="A50" s="20"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="22"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="22"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="23"/>
+      <c r="N50" s="24"/>
+      <c r="O50" s="25"/>
+      <c r="P50" s="18"/>
+      <c r="Q50" s="26"/>
+      <c r="R50" s="7"/>
+      <c r="S50" s="7"/>
+      <c r="T50" s="7"/>
+      <c r="U50" s="7"/>
+      <c r="V50" s="7"/>
+      <c r="W50" s="7"/>
     </row>
     <row r="51" ht="21.85" customHeight="1">
-      <c r="A51" s="32"/>
-      <c r="B51" s="33"/>
-      <c r="C51" s="33"/>
-      <c r="D51" s="33"/>
-      <c r="E51" s="33"/>
-      <c r="F51" s="34" cm="1">
-        <f t="array" ref="F51">SUM(F7:F7)</f>
+      <c r="A51" s="27"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="28" cm="1">
+        <f t="array" ref="F51">SUM(F7:F50)</f>
         <v>0</v>
       </c>
-      <c r="G51" s="35" cm="1">
-        <f t="array" ref="G51">SUM(G7:G7)</f>
+      <c r="G51" s="29" cm="1">
+        <f t="array" ref="G51">SUM(G7:G50)</f>
         <v>0</v>
       </c>
-      <c r="H51" s="33"/>
-      <c r="I51" s="35" cm="1">
-        <f t="array" ref="I51">SUM(I7:I7)</f>
+      <c r="H51" s="22" cm="1">
+        <f t="array" ref="H51">SUM(H7:H50)</f>
         <v>0</v>
       </c>
-      <c r="J51" s="36" cm="1">
-        <f t="array" ref="J51">SUM(J7:J7)</f>
+      <c r="I51" s="29" cm="1">
+        <f t="array" ref="I51">SUM(I7:I50)</f>
         <v>0</v>
       </c>
-      <c r="K51" s="35" cm="1">
-        <f t="array" ref="K51">SUM(K7:K7)</f>
+      <c r="J51" s="22" cm="1">
+        <f t="array" ref="J51">SUM(J7:J50)</f>
         <v>0</v>
       </c>
-      <c r="L51" s="34" cm="1">
-        <f t="array" ref="L51">SUM(L7:L7)</f>
+      <c r="K51" s="29" cm="1">
+        <f t="array" ref="K51">SUM(K7:K50)</f>
         <v>0</v>
       </c>
-      <c r="M51" s="37" cm="1">
-        <f t="array" ref="M51">SUM(M7:M7)</f>
+      <c r="L51" s="28" cm="1">
+        <f t="array" ref="L51">SUM(L7:L50)</f>
         <v>0</v>
       </c>
-      <c r="N51" s="38" cm="1">
+      <c r="M51" s="30" cm="1">
+        <f t="array" ref="M51">SUM(M7:M50)</f>
+        <v>0</v>
+      </c>
+      <c r="N51" s="31" cm="1">
         <f t="array" ref="N51">SUM(G51+I51+K51+M51)</f>
         <v>0</v>
       </c>
-      <c r="O51" s="33"/>
-      <c r="P51" s="33"/>
-      <c r="Q51" s="19"/>
-      <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4"/>
-      <c r="U51" s="4"/>
-      <c r="V51" s="4"/>
-      <c r="W51" s="4"/>
+      <c r="O51" s="6"/>
+      <c r="P51" s="6"/>
+      <c r="Q51" s="7"/>
+      <c r="R51" s="7"/>
+      <c r="S51" s="7"/>
+      <c r="T51" s="7"/>
+      <c r="U51" s="7"/>
+      <c r="V51" s="7"/>
+      <c r="W51" s="7"/>
     </row>
     <row r="52" ht="21.85" customHeight="1">
-      <c r="A52" s="39"/>
-      <c r="B52" s="40"/>
-      <c r="C52" s="40"/>
-      <c r="D52" t="s" s="41">
+      <c r="A52" s="27"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" t="s" s="12">
         <v>19</v>
       </c>
-      <c r="E52" s="42"/>
-      <c r="F52" s="40"/>
-      <c r="G52" s="40"/>
-      <c r="H52" s="40"/>
-      <c r="I52" s="40"/>
-      <c r="J52" s="40"/>
-      <c r="K52" s="40"/>
-      <c r="L52" s="43"/>
-      <c r="M52" s="44"/>
-      <c r="N52" s="40"/>
-      <c r="O52" s="40"/>
-      <c r="P52" s="40"/>
-      <c r="Q52" s="4"/>
-      <c r="R52" s="4"/>
-      <c r="S52" s="4"/>
-      <c r="T52" s="4"/>
-      <c r="U52" s="4"/>
-      <c r="V52" s="4"/>
-      <c r="W52" s="4"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="14"/>
+      <c r="N52" s="6"/>
+      <c r="O52" s="6"/>
+      <c r="P52" s="6"/>
+      <c r="Q52" s="7"/>
+      <c r="R52" s="7"/>
+      <c r="S52" s="7"/>
+      <c r="T52" s="7"/>
+      <c r="U52" s="7"/>
+      <c r="V52" s="7"/>
+      <c r="W52" s="7"/>
     </row>
     <row r="53" ht="21.85" customHeight="1">
-      <c r="A53" s="32"/>
-      <c r="B53" s="45"/>
-      <c r="C53" s="22"/>
-      <c r="D53" t="s" s="46">
+      <c r="A53" s="27"/>
+      <c r="B53" s="32"/>
+      <c r="C53" s="33"/>
+      <c r="D53" t="s" s="12">
         <v>20</v>
       </c>
-      <c r="E53" s="47"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="22"/>
-      <c r="H53" s="22"/>
-      <c r="I53" s="25"/>
-      <c r="J53" s="22"/>
-      <c r="K53" s="25"/>
-      <c r="L53" s="22"/>
-      <c r="M53" s="26"/>
-      <c r="N53" s="27"/>
-      <c r="O53" t="s" s="23">
+      <c r="E53" s="7"/>
+      <c r="F53" s="33"/>
+      <c r="G53" s="33"/>
+      <c r="H53" s="33"/>
+      <c r="I53" s="34"/>
+      <c r="J53" s="33"/>
+      <c r="K53" s="34"/>
+      <c r="L53" s="33"/>
+      <c r="M53" s="35"/>
+      <c r="N53" s="36"/>
+      <c r="O53" t="s" s="10">
         <v>21</v>
       </c>
-      <c r="P53" s="48" cm="1">
-        <f t="array" ref="P53">SUM(F51,J51,L51)</f>
+      <c r="P53" s="37" cm="1">
+        <f t="array" ref="P53">SUM(F51,J51,L51)+H51</f>
         <v>0</v>
       </c>
-      <c r="Q53" s="19"/>
-      <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
-      <c r="T53" s="4"/>
-      <c r="U53" s="4"/>
-      <c r="V53" s="4"/>
-      <c r="W53" s="4"/>
+      <c r="Q53" s="7"/>
+      <c r="R53" s="7"/>
+      <c r="S53" s="7"/>
+      <c r="T53" s="7"/>
+      <c r="U53" s="7"/>
+      <c r="V53" s="7"/>
+      <c r="W53" s="7"/>
     </row>
     <row r="54" ht="21.85" customHeight="1">
-      <c r="A54" s="32"/>
-      <c r="B54" s="45"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="47"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="22"/>
-      <c r="I54" s="25"/>
-      <c r="J54" s="22"/>
-      <c r="K54" s="25"/>
-      <c r="L54" s="22"/>
-      <c r="M54" s="26"/>
-      <c r="N54" s="27"/>
-      <c r="O54" t="s" s="23">
+      <c r="A54" s="27"/>
+      <c r="B54" s="32"/>
+      <c r="C54" s="33"/>
+      <c r="D54" s="33"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="33"/>
+      <c r="G54" s="33"/>
+      <c r="H54" s="33"/>
+      <c r="I54" s="34"/>
+      <c r="J54" s="33"/>
+      <c r="K54" s="34"/>
+      <c r="L54" s="33"/>
+      <c r="M54" s="35"/>
+      <c r="N54" s="36"/>
+      <c r="O54" t="s" s="10">
         <v>22</v>
       </c>
-      <c r="P54" s="48" cm="1">
+      <c r="P54" s="37" cm="1">
         <f t="array" ref="P54">SUM(G51+K51+M51)</f>
         <v>0</v>
       </c>
-      <c r="Q54" s="19"/>
-      <c r="R54" s="4"/>
-      <c r="S54" s="4"/>
-      <c r="T54" s="4"/>
-      <c r="U54" s="4"/>
-      <c r="V54" s="4"/>
-      <c r="W54" s="4"/>
+      <c r="Q54" s="7"/>
+      <c r="R54" s="7"/>
+      <c r="S54" s="7"/>
+      <c r="T54" s="7"/>
+      <c r="U54" s="7"/>
+      <c r="V54" s="7"/>
+      <c r="W54" s="7"/>
     </row>
     <row r="55" ht="148.75" customHeight="1">
-      <c r="A55" t="s" s="49">
+      <c r="A55" t="s" s="38">
         <v>23</v>
       </c>
-      <c r="B55" s="50"/>
-      <c r="C55" s="50"/>
-      <c r="D55" t="s" s="51">
+      <c r="B55" s="39"/>
+      <c r="C55" s="40"/>
+      <c r="D55" t="s" s="41">
         <v>24</v>
       </c>
-      <c r="E55" t="s" s="52">
+      <c r="E55" t="s" s="42">
         <v>25</v>
       </c>
-      <c r="F55" s="53"/>
-      <c r="G55" s="53"/>
-      <c r="H55" s="54"/>
-      <c r="I55" s="54"/>
-      <c r="J55" t="s" s="55">
+      <c r="F55" s="43"/>
+      <c r="G55" s="44"/>
+      <c r="H55" s="27"/>
+      <c r="I55" s="27"/>
+      <c r="J55" t="s" s="45">
         <v>26</v>
       </c>
-      <c r="K55" s="54"/>
-      <c r="L55" s="54"/>
-      <c r="M55" s="56"/>
-      <c r="N55" s="54"/>
-      <c r="O55" s="54"/>
-      <c r="P55" s="54"/>
-      <c r="Q55" s="4"/>
-      <c r="R55" s="4"/>
-      <c r="S55" s="4"/>
-      <c r="T55" s="4"/>
-      <c r="U55" s="4"/>
-      <c r="V55" s="4"/>
-      <c r="W55" s="4"/>
+      <c r="K55" s="27"/>
+      <c r="L55" s="27"/>
+      <c r="M55" s="46"/>
+      <c r="N55" s="27"/>
+      <c r="O55" s="27"/>
+      <c r="P55" s="27"/>
+      <c r="Q55" s="7"/>
+      <c r="R55" s="7"/>
+      <c r="S55" s="7"/>
+      <c r="T55" s="7"/>
+      <c r="U55" s="7"/>
+      <c r="V55" s="7"/>
+      <c r="W55" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="13">

--- a/template.xlsx
+++ b/template.xlsx
@@ -253,9 +253,7 @@
       <left style="thin">
         <color indexed="8"/>
       </left>
-      <right>
-        <color indexed="8"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="8"/>
       </top>
@@ -265,12 +263,8 @@
       <diagonal/>
     </border>
     <border>
-      <left>
-        <color indexed="8"/>
-      </left>
-      <right>
-        <color indexed="8"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
         <color indexed="8"/>
       </top>
@@ -280,9 +274,7 @@
       <diagonal/>
     </border>
     <border>
-      <left>
-        <color indexed="8"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="8"/>
       </right>
@@ -319,9 +311,7 @@
       <top style="thin">
         <color indexed="8"/>
       </top>
-      <bottom>
-        <color indexed="8"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -331,9 +321,7 @@
       <right style="thin">
         <color indexed="8"/>
       </right>
-      <top>
-        <color indexed="8"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color indexed="8"/>
       </bottom>
@@ -345,7 +333,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -367,86 +355,83 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="59" fontId="3" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="59" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="60" fontId="5" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="61" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="62" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="61" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="62" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="59" fontId="3" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="59" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="60" fontId="5" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="61" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="62" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="61" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="62" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="4" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="61" fontId="4" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
@@ -1546,15 +1531,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:W55"/>
+  <dimension ref="A1:P55"/>
   <sheetFormatPr defaultColWidth="10.8333" defaultRowHeight="14" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="10.8516" style="1" customWidth="1"/>
     <col min="2" max="2" width="7" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.8516" style="1" customWidth="1"/>
     <col min="4" max="4" width="33.3516" style="1" customWidth="1"/>
-    <col min="5" max="23" width="10.8516" style="1" customWidth="1"/>
-    <col min="24" max="16384" width="10.8516" style="1" customWidth="1"/>
+    <col min="5" max="16" width="10.8516" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="10.8516" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.6" customHeight="1">
@@ -1576,46 +1561,32 @@
       <c r="N1" s="5"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
     </row>
     <row r="2" ht="30.6" customHeight="1">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="8"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="7"/>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
     </row>
     <row r="3" ht="21.85" customHeight="1">
-      <c r="A3" t="s" s="10">
+      <c r="A3" t="s" s="9">
         <v>1</v>
       </c>
-      <c r="B3" s="11"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="6"/>
-      <c r="D3" t="s" s="10">
+      <c r="D3" t="s" s="9">
         <v>2</v>
       </c>
       <c r="E3" s="6"/>
@@ -1623,22 +1594,15 @@
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
-      <c r="J3" t="s" s="12">
+      <c r="J3" t="s" s="11">
         <v>3</v>
       </c>
-      <c r="K3" s="13"/>
+      <c r="K3" s="12"/>
       <c r="L3" s="6"/>
-      <c r="M3" s="14"/>
+      <c r="M3" s="13"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
     </row>
     <row r="4" ht="21.85" customHeight="1">
       <c r="A4" s="6"/>
@@ -1653,1269 +1617,933 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
-      <c r="M4" s="14"/>
+      <c r="M4" s="13"/>
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
     </row>
     <row r="5" ht="21.85" customHeight="1">
-      <c r="A5" t="s" s="15">
+      <c r="A5" t="s" s="14">
         <v>4</v>
       </c>
-      <c r="B5" t="s" s="15">
+      <c r="B5" t="s" s="14">
         <v>5</v>
       </c>
-      <c r="C5" t="s" s="15">
+      <c r="C5" t="s" s="14">
         <v>6</v>
       </c>
-      <c r="D5" t="s" s="15">
+      <c r="D5" t="s" s="14">
         <v>7</v>
       </c>
-      <c r="E5" t="s" s="15">
+      <c r="E5" t="s" s="14">
         <v>8</v>
       </c>
-      <c r="F5" t="s" s="16">
+      <c r="F5" t="s" s="15">
         <v>9</v>
       </c>
-      <c r="G5" s="17"/>
-      <c r="H5" t="s" s="16">
+      <c r="G5" s="16"/>
+      <c r="H5" t="s" s="15">
         <v>10</v>
       </c>
-      <c r="I5" s="17"/>
-      <c r="J5" t="s" s="16">
+      <c r="I5" s="16"/>
+      <c r="J5" t="s" s="15">
         <v>11</v>
       </c>
-      <c r="K5" s="17"/>
-      <c r="L5" t="s" s="16">
+      <c r="K5" s="16"/>
+      <c r="L5" t="s" s="15">
         <v>12</v>
       </c>
-      <c r="M5" s="17"/>
-      <c r="N5" t="s" s="18">
+      <c r="M5" s="16"/>
+      <c r="N5" t="s" s="17">
         <v>13</v>
       </c>
-      <c r="O5" t="s" s="16">
+      <c r="O5" t="s" s="15">
         <v>14</v>
       </c>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
+      <c r="P5" s="16"/>
     </row>
     <row r="6" ht="21.85" customHeight="1">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" t="s" s="18">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" t="s" s="17">
         <v>15</v>
       </c>
-      <c r="G6" t="s" s="18">
+      <c r="G6" t="s" s="17">
         <v>16</v>
       </c>
-      <c r="H6" t="s" s="18">
+      <c r="H6" t="s" s="17">
         <v>15</v>
       </c>
-      <c r="I6" t="s" s="18">
+      <c r="I6" t="s" s="17">
         <v>16</v>
       </c>
-      <c r="J6" t="s" s="18">
+      <c r="J6" t="s" s="17">
         <v>15</v>
       </c>
-      <c r="K6" t="s" s="18">
+      <c r="K6" t="s" s="17">
         <v>16</v>
       </c>
-      <c r="L6" t="s" s="18">
+      <c r="L6" t="s" s="17">
         <v>15</v>
       </c>
-      <c r="M6" t="s" s="18">
+      <c r="M6" t="s" s="17">
         <v>16</v>
       </c>
-      <c r="N6" t="s" s="18">
+      <c r="N6" t="s" s="17">
         <v>16</v>
       </c>
-      <c r="O6" t="s" s="18">
+      <c r="O6" t="s" s="17">
         <v>17</v>
       </c>
-      <c r="P6" t="s" s="18">
+      <c r="P6" t="s" s="17">
         <v>18</v>
       </c>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
     </row>
     <row r="7" ht="21.85" customHeight="1">
-      <c r="A7" s="20"/>
+      <c r="A7" s="19"/>
       <c r="B7" s="6"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="10"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="9"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
-      <c r="I7" s="22"/>
+      <c r="I7" s="21"/>
       <c r="J7" s="6"/>
-      <c r="K7" s="22"/>
+      <c r="K7" s="21"/>
       <c r="L7" s="6"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="25"/>
-      <c r="P7" s="18"/>
-      <c r="Q7" s="26"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="17"/>
     </row>
     <row r="8" ht="21.85" customHeight="1">
-      <c r="A8" s="20"/>
+      <c r="A8" s="19"/>
       <c r="B8" s="6"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="10"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="9"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
-      <c r="I8" s="22"/>
+      <c r="I8" s="21"/>
       <c r="J8" s="6"/>
-      <c r="K8" s="22"/>
+      <c r="K8" s="21"/>
       <c r="L8" s="6"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="25"/>
-      <c r="P8" s="18"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="17"/>
     </row>
     <row r="9" ht="21.85" customHeight="1">
-      <c r="A9" s="20"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="6"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="10"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="9"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
-      <c r="I9" s="22"/>
+      <c r="I9" s="21"/>
       <c r="J9" s="6"/>
-      <c r="K9" s="22"/>
+      <c r="K9" s="21"/>
       <c r="L9" s="6"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="17"/>
     </row>
     <row r="10" ht="21.85" customHeight="1">
-      <c r="A10" s="20"/>
+      <c r="A10" s="19"/>
       <c r="B10" s="6"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="10"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="9"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
-      <c r="I10" s="22"/>
+      <c r="I10" s="21"/>
       <c r="J10" s="6"/>
-      <c r="K10" s="22"/>
+      <c r="K10" s="21"/>
       <c r="L10" s="6"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="25"/>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="17"/>
     </row>
     <row r="11" ht="21.85" customHeight="1">
-      <c r="A11" s="20"/>
+      <c r="A11" s="19"/>
       <c r="B11" s="6"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="10"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="9"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
-      <c r="I11" s="22"/>
+      <c r="I11" s="21"/>
       <c r="J11" s="6"/>
-      <c r="K11" s="22"/>
+      <c r="K11" s="21"/>
       <c r="L11" s="6"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="24"/>
-      <c r="O11" s="25"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="26"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="17"/>
     </row>
     <row r="12" ht="21.85" customHeight="1">
-      <c r="A12" s="20"/>
+      <c r="A12" s="19"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="10"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="9"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
-      <c r="I12" s="22"/>
+      <c r="I12" s="21"/>
       <c r="J12" s="6"/>
-      <c r="K12" s="22"/>
+      <c r="K12" s="21"/>
       <c r="L12" s="6"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="25"/>
-      <c r="P12" s="18"/>
-      <c r="Q12" s="26"/>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="17"/>
     </row>
     <row r="13" ht="21.85" customHeight="1">
-      <c r="A13" s="20"/>
+      <c r="A13" s="19"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="10"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="9"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
-      <c r="I13" s="22"/>
+      <c r="I13" s="21"/>
       <c r="J13" s="6"/>
-      <c r="K13" s="22"/>
+      <c r="K13" s="21"/>
       <c r="L13" s="6"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="25"/>
-      <c r="P13" s="18"/>
-      <c r="Q13" s="26"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="17"/>
     </row>
     <row r="14" ht="21.85" customHeight="1">
-      <c r="A14" s="20"/>
+      <c r="A14" s="19"/>
       <c r="B14" s="6"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="10"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="9"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
-      <c r="I14" s="22"/>
+      <c r="I14" s="21"/>
       <c r="J14" s="6"/>
-      <c r="K14" s="22"/>
+      <c r="K14" s="21"/>
       <c r="L14" s="6"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="25"/>
-      <c r="P14" s="18"/>
-      <c r="Q14" s="26"/>
-      <c r="R14" s="7"/>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="7"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="17"/>
     </row>
     <row r="15" ht="21.85" customHeight="1">
-      <c r="A15" s="20"/>
+      <c r="A15" s="19"/>
       <c r="B15" s="6"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="10"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="9"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
-      <c r="I15" s="22"/>
+      <c r="I15" s="21"/>
       <c r="J15" s="6"/>
-      <c r="K15" s="22"/>
+      <c r="K15" s="21"/>
       <c r="L15" s="6"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="25"/>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="26"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="7"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="17"/>
     </row>
     <row r="16" ht="21.85" customHeight="1">
-      <c r="A16" s="20"/>
+      <c r="A16" s="19"/>
       <c r="B16" s="6"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="10"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="9"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
-      <c r="I16" s="22"/>
+      <c r="I16" s="21"/>
       <c r="J16" s="6"/>
-      <c r="K16" s="22"/>
+      <c r="K16" s="21"/>
       <c r="L16" s="6"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="25"/>
-      <c r="P16" s="18"/>
-      <c r="Q16" s="26"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="17"/>
     </row>
     <row r="17" ht="21.85" customHeight="1">
-      <c r="A17" s="20"/>
+      <c r="A17" s="19"/>
       <c r="B17" s="6"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="10"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="9"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
-      <c r="I17" s="22"/>
+      <c r="I17" s="21"/>
       <c r="J17" s="6"/>
-      <c r="K17" s="22"/>
+      <c r="K17" s="21"/>
       <c r="L17" s="6"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="25"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="26"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="7"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="17"/>
     </row>
     <row r="18" ht="21.85" customHeight="1">
-      <c r="A18" s="20"/>
+      <c r="A18" s="19"/>
       <c r="B18" s="6"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="10"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="9"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
-      <c r="I18" s="22"/>
+      <c r="I18" s="21"/>
       <c r="J18" s="6"/>
-      <c r="K18" s="22"/>
+      <c r="K18" s="21"/>
       <c r="L18" s="6"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="24"/>
-      <c r="O18" s="25"/>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="26"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="7"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="17"/>
     </row>
     <row r="19" ht="21.85" customHeight="1">
-      <c r="A19" s="20"/>
+      <c r="A19" s="19"/>
       <c r="B19" s="6"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="10"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="9"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
-      <c r="I19" s="22"/>
+      <c r="I19" s="21"/>
       <c r="J19" s="6"/>
-      <c r="K19" s="22"/>
+      <c r="K19" s="21"/>
       <c r="L19" s="6"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="25"/>
-      <c r="P19" s="18"/>
-      <c r="Q19" s="26"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="7"/>
+      <c r="M19" s="22"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="17"/>
     </row>
     <row r="20" ht="21.85" customHeight="1">
-      <c r="A20" s="20"/>
+      <c r="A20" s="19"/>
       <c r="B20" s="6"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="10"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="9"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
-      <c r="I20" s="22"/>
+      <c r="I20" s="21"/>
       <c r="J20" s="6"/>
-      <c r="K20" s="22"/>
+      <c r="K20" s="21"/>
       <c r="L20" s="6"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="25"/>
-      <c r="P20" s="18"/>
-      <c r="Q20" s="26"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
-      <c r="V20" s="7"/>
-      <c r="W20" s="7"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="17"/>
     </row>
     <row r="21" ht="21.85" customHeight="1">
-      <c r="A21" s="20"/>
+      <c r="A21" s="19"/>
       <c r="B21" s="6"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="10"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="9"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
-      <c r="I21" s="22"/>
+      <c r="I21" s="21"/>
       <c r="J21" s="6"/>
-      <c r="K21" s="22"/>
+      <c r="K21" s="21"/>
       <c r="L21" s="6"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="25"/>
-      <c r="P21" s="18"/>
-      <c r="Q21" s="26"/>
-      <c r="R21" s="7"/>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="7"/>
-      <c r="V21" s="7"/>
-      <c r="W21" s="7"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="24"/>
+      <c r="P21" s="17"/>
     </row>
     <row r="22" ht="21.85" customHeight="1">
-      <c r="A22" s="20"/>
+      <c r="A22" s="19"/>
       <c r="B22" s="6"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="10"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="9"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
-      <c r="I22" s="22"/>
+      <c r="I22" s="21"/>
       <c r="J22" s="6"/>
-      <c r="K22" s="22"/>
+      <c r="K22" s="21"/>
       <c r="L22" s="6"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="24"/>
-      <c r="O22" s="25"/>
-      <c r="P22" s="18"/>
-      <c r="Q22" s="26"/>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
-      <c r="W22" s="7"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="17"/>
     </row>
     <row r="23" ht="21.85" customHeight="1">
-      <c r="A23" s="20"/>
+      <c r="A23" s="19"/>
       <c r="B23" s="6"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="10"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="9"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
-      <c r="I23" s="22"/>
+      <c r="I23" s="21"/>
       <c r="J23" s="6"/>
-      <c r="K23" s="22"/>
+      <c r="K23" s="21"/>
       <c r="L23" s="6"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="25"/>
-      <c r="P23" s="18"/>
-      <c r="Q23" s="26"/>
-      <c r="R23" s="7"/>
-      <c r="S23" s="7"/>
-      <c r="T23" s="7"/>
-      <c r="U23" s="7"/>
-      <c r="V23" s="7"/>
-      <c r="W23" s="7"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="17"/>
     </row>
     <row r="24" ht="21.85" customHeight="1">
-      <c r="A24" s="20"/>
+      <c r="A24" s="19"/>
       <c r="B24" s="6"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="10"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="9"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
-      <c r="I24" s="22"/>
+      <c r="I24" s="21"/>
       <c r="J24" s="6"/>
-      <c r="K24" s="22"/>
+      <c r="K24" s="21"/>
       <c r="L24" s="6"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="24"/>
-      <c r="O24" s="25"/>
-      <c r="P24" s="18"/>
-      <c r="Q24" s="26"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="7"/>
-      <c r="T24" s="7"/>
-      <c r="U24" s="7"/>
-      <c r="V24" s="7"/>
-      <c r="W24" s="7"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="23"/>
+      <c r="O24" s="24"/>
+      <c r="P24" s="17"/>
     </row>
     <row r="25" ht="21.85" customHeight="1">
-      <c r="A25" s="20"/>
+      <c r="A25" s="19"/>
       <c r="B25" s="6"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="10"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="9"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
-      <c r="I25" s="22"/>
+      <c r="I25" s="21"/>
       <c r="J25" s="6"/>
-      <c r="K25" s="22"/>
+      <c r="K25" s="21"/>
       <c r="L25" s="6"/>
-      <c r="M25" s="23"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="25"/>
-      <c r="P25" s="18"/>
-      <c r="Q25" s="26"/>
-      <c r="R25" s="7"/>
-      <c r="S25" s="7"/>
-      <c r="T25" s="7"/>
-      <c r="U25" s="7"/>
-      <c r="V25" s="7"/>
-      <c r="W25" s="7"/>
+      <c r="M25" s="22"/>
+      <c r="N25" s="23"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="17"/>
     </row>
     <row r="26" ht="21.85" customHeight="1">
-      <c r="A26" s="20"/>
+      <c r="A26" s="19"/>
       <c r="B26" s="6"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="10"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="9"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
-      <c r="I26" s="22"/>
+      <c r="I26" s="21"/>
       <c r="J26" s="6"/>
-      <c r="K26" s="22"/>
+      <c r="K26" s="21"/>
       <c r="L26" s="6"/>
-      <c r="M26" s="23"/>
-      <c r="N26" s="24"/>
-      <c r="O26" s="25"/>
-      <c r="P26" s="18"/>
-      <c r="Q26" s="26"/>
-      <c r="R26" s="7"/>
-      <c r="S26" s="7"/>
-      <c r="T26" s="7"/>
-      <c r="U26" s="7"/>
-      <c r="V26" s="7"/>
-      <c r="W26" s="7"/>
+      <c r="M26" s="22"/>
+      <c r="N26" s="23"/>
+      <c r="O26" s="24"/>
+      <c r="P26" s="17"/>
     </row>
     <row r="27" ht="21.85" customHeight="1">
-      <c r="A27" s="20"/>
+      <c r="A27" s="19"/>
       <c r="B27" s="6"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="10"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="9"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
-      <c r="I27" s="22"/>
+      <c r="I27" s="21"/>
       <c r="J27" s="6"/>
-      <c r="K27" s="22"/>
+      <c r="K27" s="21"/>
       <c r="L27" s="6"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="24"/>
-      <c r="O27" s="25"/>
-      <c r="P27" s="18"/>
-      <c r="Q27" s="26"/>
-      <c r="R27" s="7"/>
-      <c r="S27" s="7"/>
-      <c r="T27" s="7"/>
-      <c r="U27" s="7"/>
-      <c r="V27" s="7"/>
-      <c r="W27" s="7"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="23"/>
+      <c r="O27" s="24"/>
+      <c r="P27" s="17"/>
     </row>
     <row r="28" ht="21.85" customHeight="1">
-      <c r="A28" s="20"/>
+      <c r="A28" s="19"/>
       <c r="B28" s="6"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="10"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="9"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
-      <c r="I28" s="22"/>
+      <c r="I28" s="21"/>
       <c r="J28" s="6"/>
-      <c r="K28" s="22"/>
+      <c r="K28" s="21"/>
       <c r="L28" s="6"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="24"/>
-      <c r="O28" s="25"/>
-      <c r="P28" s="18"/>
-      <c r="Q28" s="26"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="7"/>
-      <c r="T28" s="7"/>
-      <c r="U28" s="7"/>
-      <c r="V28" s="7"/>
-      <c r="W28" s="7"/>
+      <c r="M28" s="22"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="24"/>
+      <c r="P28" s="17"/>
     </row>
     <row r="29" ht="21.85" customHeight="1">
-      <c r="A29" s="20"/>
+      <c r="A29" s="19"/>
       <c r="B29" s="6"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="10"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="9"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
-      <c r="I29" s="22"/>
+      <c r="I29" s="21"/>
       <c r="J29" s="6"/>
-      <c r="K29" s="22"/>
+      <c r="K29" s="21"/>
       <c r="L29" s="6"/>
-      <c r="M29" s="23"/>
-      <c r="N29" s="24"/>
-      <c r="O29" s="25"/>
-      <c r="P29" s="18"/>
-      <c r="Q29" s="26"/>
-      <c r="R29" s="7"/>
-      <c r="S29" s="7"/>
-      <c r="T29" s="7"/>
-      <c r="U29" s="7"/>
-      <c r="V29" s="7"/>
-      <c r="W29" s="7"/>
+      <c r="M29" s="22"/>
+      <c r="N29" s="23"/>
+      <c r="O29" s="24"/>
+      <c r="P29" s="17"/>
     </row>
     <row r="30" ht="21.85" customHeight="1">
-      <c r="A30" s="20"/>
+      <c r="A30" s="19"/>
       <c r="B30" s="6"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="10"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="9"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
-      <c r="I30" s="22"/>
+      <c r="I30" s="21"/>
       <c r="J30" s="6"/>
-      <c r="K30" s="22"/>
+      <c r="K30" s="21"/>
       <c r="L30" s="6"/>
-      <c r="M30" s="23"/>
-      <c r="N30" s="24"/>
-      <c r="O30" s="25"/>
-      <c r="P30" s="18"/>
-      <c r="Q30" s="26"/>
-      <c r="R30" s="7"/>
-      <c r="S30" s="7"/>
-      <c r="T30" s="7"/>
-      <c r="U30" s="7"/>
-      <c r="V30" s="7"/>
-      <c r="W30" s="7"/>
+      <c r="M30" s="22"/>
+      <c r="N30" s="23"/>
+      <c r="O30" s="24"/>
+      <c r="P30" s="17"/>
     </row>
     <row r="31" ht="21.85" customHeight="1">
-      <c r="A31" s="20"/>
+      <c r="A31" s="19"/>
       <c r="B31" s="6"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="10"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="9"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
-      <c r="I31" s="22"/>
+      <c r="I31" s="21"/>
       <c r="J31" s="6"/>
-      <c r="K31" s="22"/>
+      <c r="K31" s="21"/>
       <c r="L31" s="6"/>
-      <c r="M31" s="23"/>
-      <c r="N31" s="24"/>
-      <c r="O31" s="25"/>
-      <c r="P31" s="18"/>
-      <c r="Q31" s="26"/>
-      <c r="R31" s="7"/>
-      <c r="S31" s="7"/>
-      <c r="T31" s="7"/>
-      <c r="U31" s="7"/>
-      <c r="V31" s="7"/>
-      <c r="W31" s="7"/>
+      <c r="M31" s="22"/>
+      <c r="N31" s="23"/>
+      <c r="O31" s="24"/>
+      <c r="P31" s="17"/>
     </row>
     <row r="32" ht="21.85" customHeight="1">
-      <c r="A32" s="20"/>
+      <c r="A32" s="19"/>
       <c r="B32" s="6"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="10"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="9"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
-      <c r="I32" s="22"/>
+      <c r="I32" s="21"/>
       <c r="J32" s="6"/>
-      <c r="K32" s="22"/>
+      <c r="K32" s="21"/>
       <c r="L32" s="6"/>
-      <c r="M32" s="23"/>
-      <c r="N32" s="24"/>
-      <c r="O32" s="25"/>
-      <c r="P32" s="18"/>
-      <c r="Q32" s="26"/>
-      <c r="R32" s="7"/>
-      <c r="S32" s="7"/>
-      <c r="T32" s="7"/>
-      <c r="U32" s="7"/>
-      <c r="V32" s="7"/>
-      <c r="W32" s="7"/>
+      <c r="M32" s="22"/>
+      <c r="N32" s="23"/>
+      <c r="O32" s="24"/>
+      <c r="P32" s="17"/>
     </row>
     <row r="33" ht="21.85" customHeight="1">
-      <c r="A33" s="20"/>
+      <c r="A33" s="19"/>
       <c r="B33" s="6"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="10"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="9"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
-      <c r="I33" s="22"/>
+      <c r="I33" s="21"/>
       <c r="J33" s="6"/>
-      <c r="K33" s="22"/>
+      <c r="K33" s="21"/>
       <c r="L33" s="6"/>
-      <c r="M33" s="23"/>
-      <c r="N33" s="24"/>
-      <c r="O33" s="25"/>
-      <c r="P33" s="18"/>
-      <c r="Q33" s="26"/>
-      <c r="R33" s="7"/>
-      <c r="S33" s="7"/>
-      <c r="T33" s="7"/>
-      <c r="U33" s="7"/>
-      <c r="V33" s="7"/>
-      <c r="W33" s="7"/>
+      <c r="M33" s="22"/>
+      <c r="N33" s="23"/>
+      <c r="O33" s="24"/>
+      <c r="P33" s="17"/>
     </row>
     <row r="34" ht="21.85" customHeight="1">
-      <c r="A34" s="20"/>
+      <c r="A34" s="19"/>
       <c r="B34" s="6"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="10"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="9"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
-      <c r="I34" s="22"/>
+      <c r="I34" s="21"/>
       <c r="J34" s="6"/>
-      <c r="K34" s="22"/>
+      <c r="K34" s="21"/>
       <c r="L34" s="6"/>
-      <c r="M34" s="23"/>
-      <c r="N34" s="24"/>
-      <c r="O34" s="25"/>
-      <c r="P34" s="18"/>
-      <c r="Q34" s="26"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="7"/>
-      <c r="T34" s="7"/>
-      <c r="U34" s="7"/>
-      <c r="V34" s="7"/>
-      <c r="W34" s="7"/>
+      <c r="M34" s="22"/>
+      <c r="N34" s="23"/>
+      <c r="O34" s="24"/>
+      <c r="P34" s="17"/>
     </row>
     <row r="35" ht="21.85" customHeight="1">
-      <c r="A35" s="20"/>
+      <c r="A35" s="19"/>
       <c r="B35" s="6"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="10"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="9"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
-      <c r="I35" s="22"/>
+      <c r="I35" s="21"/>
       <c r="J35" s="6"/>
-      <c r="K35" s="22"/>
+      <c r="K35" s="21"/>
       <c r="L35" s="6"/>
-      <c r="M35" s="23"/>
-      <c r="N35" s="24"/>
-      <c r="O35" s="25"/>
-      <c r="P35" s="18"/>
-      <c r="Q35" s="26"/>
-      <c r="R35" s="7"/>
-      <c r="S35" s="7"/>
-      <c r="T35" s="7"/>
-      <c r="U35" s="7"/>
-      <c r="V35" s="7"/>
-      <c r="W35" s="7"/>
+      <c r="M35" s="22"/>
+      <c r="N35" s="23"/>
+      <c r="O35" s="24"/>
+      <c r="P35" s="17"/>
     </row>
     <row r="36" ht="21.85" customHeight="1">
-      <c r="A36" s="20"/>
+      <c r="A36" s="19"/>
       <c r="B36" s="6"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="10"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="9"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
-      <c r="I36" s="22"/>
+      <c r="I36" s="21"/>
       <c r="J36" s="6"/>
-      <c r="K36" s="22"/>
+      <c r="K36" s="21"/>
       <c r="L36" s="6"/>
-      <c r="M36" s="23"/>
-      <c r="N36" s="24"/>
-      <c r="O36" s="25"/>
-      <c r="P36" s="18"/>
-      <c r="Q36" s="26"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="7"/>
-      <c r="T36" s="7"/>
-      <c r="U36" s="7"/>
-      <c r="V36" s="7"/>
-      <c r="W36" s="7"/>
+      <c r="M36" s="22"/>
+      <c r="N36" s="23"/>
+      <c r="O36" s="24"/>
+      <c r="P36" s="17"/>
     </row>
     <row r="37" ht="21.85" customHeight="1">
-      <c r="A37" s="20"/>
+      <c r="A37" s="19"/>
       <c r="B37" s="6"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="10"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="9"/>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
-      <c r="I37" s="22"/>
+      <c r="I37" s="21"/>
       <c r="J37" s="6"/>
-      <c r="K37" s="22"/>
+      <c r="K37" s="21"/>
       <c r="L37" s="6"/>
-      <c r="M37" s="23"/>
-      <c r="N37" s="24"/>
-      <c r="O37" s="25"/>
-      <c r="P37" s="18"/>
-      <c r="Q37" s="26"/>
-      <c r="R37" s="7"/>
-      <c r="S37" s="7"/>
-      <c r="T37" s="7"/>
-      <c r="U37" s="7"/>
-      <c r="V37" s="7"/>
-      <c r="W37" s="7"/>
+      <c r="M37" s="22"/>
+      <c r="N37" s="23"/>
+      <c r="O37" s="24"/>
+      <c r="P37" s="17"/>
     </row>
     <row r="38" ht="21.85" customHeight="1">
-      <c r="A38" s="20"/>
+      <c r="A38" s="19"/>
       <c r="B38" s="6"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="10"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="9"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
-      <c r="I38" s="22"/>
+      <c r="I38" s="21"/>
       <c r="J38" s="6"/>
-      <c r="K38" s="22"/>
+      <c r="K38" s="21"/>
       <c r="L38" s="6"/>
-      <c r="M38" s="23"/>
-      <c r="N38" s="24"/>
-      <c r="O38" s="25"/>
-      <c r="P38" s="18"/>
-      <c r="Q38" s="26"/>
-      <c r="R38" s="7"/>
-      <c r="S38" s="7"/>
-      <c r="T38" s="7"/>
-      <c r="U38" s="7"/>
-      <c r="V38" s="7"/>
-      <c r="W38" s="7"/>
+      <c r="M38" s="22"/>
+      <c r="N38" s="23"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="17"/>
     </row>
     <row r="39" ht="21.85" customHeight="1">
-      <c r="A39" s="20"/>
+      <c r="A39" s="19"/>
       <c r="B39" s="6"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="10"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="9"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
-      <c r="I39" s="22"/>
+      <c r="I39" s="21"/>
       <c r="J39" s="6"/>
-      <c r="K39" s="22"/>
+      <c r="K39" s="21"/>
       <c r="L39" s="6"/>
-      <c r="M39" s="23"/>
-      <c r="N39" s="24"/>
-      <c r="O39" s="25"/>
-      <c r="P39" s="18"/>
-      <c r="Q39" s="26"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="7"/>
-      <c r="T39" s="7"/>
-      <c r="U39" s="7"/>
-      <c r="V39" s="7"/>
-      <c r="W39" s="7"/>
+      <c r="M39" s="22"/>
+      <c r="N39" s="23"/>
+      <c r="O39" s="24"/>
+      <c r="P39" s="17"/>
     </row>
     <row r="40" ht="21.85" customHeight="1">
-      <c r="A40" s="20"/>
+      <c r="A40" s="19"/>
       <c r="B40" s="6"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="10"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="9"/>
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
-      <c r="I40" s="22"/>
+      <c r="I40" s="21"/>
       <c r="J40" s="6"/>
-      <c r="K40" s="22"/>
+      <c r="K40" s="21"/>
       <c r="L40" s="6"/>
-      <c r="M40" s="23"/>
-      <c r="N40" s="24"/>
-      <c r="O40" s="25"/>
-      <c r="P40" s="18"/>
-      <c r="Q40" s="26"/>
-      <c r="R40" s="7"/>
-      <c r="S40" s="7"/>
-      <c r="T40" s="7"/>
-      <c r="U40" s="7"/>
-      <c r="V40" s="7"/>
-      <c r="W40" s="7"/>
+      <c r="M40" s="22"/>
+      <c r="N40" s="23"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="17"/>
     </row>
     <row r="41" ht="21.85" customHeight="1">
-      <c r="A41" s="20"/>
+      <c r="A41" s="19"/>
       <c r="B41" s="6"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="10"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="9"/>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
-      <c r="I41" s="22"/>
+      <c r="I41" s="21"/>
       <c r="J41" s="6"/>
-      <c r="K41" s="22"/>
+      <c r="K41" s="21"/>
       <c r="L41" s="6"/>
-      <c r="M41" s="23"/>
-      <c r="N41" s="24"/>
-      <c r="O41" s="25"/>
-      <c r="P41" s="18"/>
-      <c r="Q41" s="26"/>
-      <c r="R41" s="7"/>
-      <c r="S41" s="7"/>
-      <c r="T41" s="7"/>
-      <c r="U41" s="7"/>
-      <c r="V41" s="7"/>
-      <c r="W41" s="7"/>
+      <c r="M41" s="22"/>
+      <c r="N41" s="23"/>
+      <c r="O41" s="24"/>
+      <c r="P41" s="17"/>
     </row>
     <row r="42" ht="21.85" customHeight="1">
-      <c r="A42" s="20"/>
+      <c r="A42" s="19"/>
       <c r="B42" s="6"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="10"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="9"/>
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
-      <c r="I42" s="22"/>
+      <c r="I42" s="21"/>
       <c r="J42" s="6"/>
-      <c r="K42" s="22"/>
+      <c r="K42" s="21"/>
       <c r="L42" s="6"/>
-      <c r="M42" s="23"/>
-      <c r="N42" s="24"/>
-      <c r="O42" s="25"/>
-      <c r="P42" s="18"/>
-      <c r="Q42" s="26"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="7"/>
-      <c r="T42" s="7"/>
-      <c r="U42" s="7"/>
-      <c r="V42" s="7"/>
-      <c r="W42" s="7"/>
+      <c r="M42" s="22"/>
+      <c r="N42" s="23"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="17"/>
     </row>
     <row r="43" ht="21.85" customHeight="1">
-      <c r="A43" s="20"/>
+      <c r="A43" s="19"/>
       <c r="B43" s="6"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="10"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="9"/>
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
-      <c r="I43" s="22"/>
+      <c r="I43" s="21"/>
       <c r="J43" s="6"/>
-      <c r="K43" s="22"/>
+      <c r="K43" s="21"/>
       <c r="L43" s="6"/>
-      <c r="M43" s="23"/>
-      <c r="N43" s="24"/>
-      <c r="O43" s="25"/>
-      <c r="P43" s="18"/>
-      <c r="Q43" s="26"/>
-      <c r="R43" s="7"/>
-      <c r="S43" s="7"/>
-      <c r="T43" s="7"/>
-      <c r="U43" s="7"/>
-      <c r="V43" s="7"/>
-      <c r="W43" s="7"/>
+      <c r="M43" s="22"/>
+      <c r="N43" s="23"/>
+      <c r="O43" s="24"/>
+      <c r="P43" s="17"/>
     </row>
     <row r="44" ht="21.85" customHeight="1">
-      <c r="A44" s="20"/>
+      <c r="A44" s="19"/>
       <c r="B44" s="6"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="10"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="9"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
-      <c r="I44" s="22"/>
+      <c r="I44" s="21"/>
       <c r="J44" s="6"/>
-      <c r="K44" s="22"/>
+      <c r="K44" s="21"/>
       <c r="L44" s="6"/>
-      <c r="M44" s="23"/>
-      <c r="N44" s="24"/>
-      <c r="O44" s="25"/>
-      <c r="P44" s="18"/>
-      <c r="Q44" s="26"/>
-      <c r="R44" s="7"/>
-      <c r="S44" s="7"/>
-      <c r="T44" s="7"/>
-      <c r="U44" s="7"/>
-      <c r="V44" s="7"/>
-      <c r="W44" s="7"/>
+      <c r="M44" s="22"/>
+      <c r="N44" s="23"/>
+      <c r="O44" s="24"/>
+      <c r="P44" s="17"/>
     </row>
     <row r="45" ht="21.85" customHeight="1">
-      <c r="A45" s="20"/>
+      <c r="A45" s="19"/>
       <c r="B45" s="6"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="10"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="9"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
-      <c r="I45" s="22"/>
+      <c r="I45" s="21"/>
       <c r="J45" s="6"/>
-      <c r="K45" s="22"/>
+      <c r="K45" s="21"/>
       <c r="L45" s="6"/>
-      <c r="M45" s="23"/>
-      <c r="N45" s="24"/>
-      <c r="O45" s="25"/>
-      <c r="P45" s="18"/>
-      <c r="Q45" s="26"/>
-      <c r="R45" s="7"/>
-      <c r="S45" s="7"/>
-      <c r="T45" s="7"/>
-      <c r="U45" s="7"/>
-      <c r="V45" s="7"/>
-      <c r="W45" s="7"/>
+      <c r="M45" s="22"/>
+      <c r="N45" s="23"/>
+      <c r="O45" s="24"/>
+      <c r="P45" s="17"/>
     </row>
     <row r="46" ht="21.85" customHeight="1">
-      <c r="A46" s="20"/>
+      <c r="A46" s="19"/>
       <c r="B46" s="6"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="10"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="9"/>
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
-      <c r="I46" s="22"/>
+      <c r="I46" s="21"/>
       <c r="J46" s="6"/>
-      <c r="K46" s="22"/>
+      <c r="K46" s="21"/>
       <c r="L46" s="6"/>
-      <c r="M46" s="23"/>
-      <c r="N46" s="24"/>
-      <c r="O46" s="25"/>
-      <c r="P46" s="18"/>
-      <c r="Q46" s="26"/>
-      <c r="R46" s="7"/>
-      <c r="S46" s="7"/>
-      <c r="T46" s="7"/>
-      <c r="U46" s="7"/>
-      <c r="V46" s="7"/>
-      <c r="W46" s="7"/>
+      <c r="M46" s="22"/>
+      <c r="N46" s="23"/>
+      <c r="O46" s="24"/>
+      <c r="P46" s="17"/>
     </row>
     <row r="47" ht="21.85" customHeight="1">
-      <c r="A47" s="20"/>
+      <c r="A47" s="19"/>
       <c r="B47" s="6"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="10"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="9"/>
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
-      <c r="I47" s="22"/>
+      <c r="I47" s="21"/>
       <c r="J47" s="6"/>
-      <c r="K47" s="22"/>
+      <c r="K47" s="21"/>
       <c r="L47" s="6"/>
-      <c r="M47" s="23"/>
-      <c r="N47" s="24"/>
-      <c r="O47" s="25"/>
-      <c r="P47" s="18"/>
-      <c r="Q47" s="26"/>
-      <c r="R47" s="7"/>
-      <c r="S47" s="7"/>
-      <c r="T47" s="7"/>
-      <c r="U47" s="7"/>
-      <c r="V47" s="7"/>
-      <c r="W47" s="7"/>
+      <c r="M47" s="22"/>
+      <c r="N47" s="23"/>
+      <c r="O47" s="24"/>
+      <c r="P47" s="17"/>
     </row>
     <row r="48" ht="21.85" customHeight="1">
-      <c r="A48" s="20"/>
+      <c r="A48" s="19"/>
       <c r="B48" s="6"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="10"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="9"/>
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
-      <c r="I48" s="22"/>
+      <c r="I48" s="21"/>
       <c r="J48" s="6"/>
-      <c r="K48" s="22"/>
+      <c r="K48" s="21"/>
       <c r="L48" s="6"/>
-      <c r="M48" s="23"/>
-      <c r="N48" s="24"/>
-      <c r="O48" s="25"/>
-      <c r="P48" s="18"/>
-      <c r="Q48" s="26"/>
-      <c r="R48" s="7"/>
-      <c r="S48" s="7"/>
-      <c r="T48" s="7"/>
-      <c r="U48" s="7"/>
-      <c r="V48" s="7"/>
-      <c r="W48" s="7"/>
+      <c r="M48" s="22"/>
+      <c r="N48" s="23"/>
+      <c r="O48" s="24"/>
+      <c r="P48" s="17"/>
     </row>
     <row r="49" ht="21.85" customHeight="1">
-      <c r="A49" s="20"/>
+      <c r="A49" s="19"/>
       <c r="B49" s="6"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="10"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="9"/>
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
-      <c r="I49" s="22"/>
+      <c r="I49" s="21"/>
       <c r="J49" s="6"/>
-      <c r="K49" s="22"/>
+      <c r="K49" s="21"/>
       <c r="L49" s="6"/>
-      <c r="M49" s="23"/>
-      <c r="N49" s="24"/>
-      <c r="O49" s="25"/>
-      <c r="P49" s="18"/>
-      <c r="Q49" s="26"/>
-      <c r="R49" s="7"/>
-      <c r="S49" s="7"/>
-      <c r="T49" s="7"/>
-      <c r="U49" s="7"/>
-      <c r="V49" s="7"/>
-      <c r="W49" s="7"/>
+      <c r="M49" s="22"/>
+      <c r="N49" s="23"/>
+      <c r="O49" s="24"/>
+      <c r="P49" s="17"/>
     </row>
     <row r="50" ht="21.85" customHeight="1">
-      <c r="A50" s="20"/>
+      <c r="A50" s="19"/>
       <c r="B50" s="6"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="10"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="9"/>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
       <c r="H50" s="6"/>
-      <c r="I50" s="22"/>
+      <c r="I50" s="21"/>
       <c r="J50" s="6"/>
-      <c r="K50" s="22"/>
+      <c r="K50" s="21"/>
       <c r="L50" s="6"/>
-      <c r="M50" s="23"/>
-      <c r="N50" s="24"/>
-      <c r="O50" s="25"/>
-      <c r="P50" s="18"/>
-      <c r="Q50" s="26"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="7"/>
-      <c r="T50" s="7"/>
-      <c r="U50" s="7"/>
-      <c r="V50" s="7"/>
-      <c r="W50" s="7"/>
+      <c r="M50" s="22"/>
+      <c r="N50" s="23"/>
+      <c r="O50" s="24"/>
+      <c r="P50" s="17"/>
     </row>
     <row r="51" ht="21.85" customHeight="1">
-      <c r="A51" s="27"/>
+      <c r="A51" s="25"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
-      <c r="F51" s="28" cm="1">
+      <c r="F51" s="26" cm="1">
         <f t="array" ref="F51">SUM(F7:F50)</f>
         <v>0</v>
       </c>
-      <c r="G51" s="29" cm="1">
+      <c r="G51" s="27" cm="1">
         <f t="array" ref="G51">SUM(G7:G50)</f>
         <v>0</v>
       </c>
-      <c r="H51" s="22" cm="1">
+      <c r="H51" s="21" cm="1">
         <f t="array" ref="H51">SUM(H7:H50)</f>
         <v>0</v>
       </c>
-      <c r="I51" s="29" cm="1">
+      <c r="I51" s="27" cm="1">
         <f t="array" ref="I51">SUM(I7:I50)</f>
         <v>0</v>
       </c>
-      <c r="J51" s="22" cm="1">
+      <c r="J51" s="21" cm="1">
         <f t="array" ref="J51">SUM(J7:J50)</f>
         <v>0</v>
       </c>
-      <c r="K51" s="29" cm="1">
+      <c r="K51" s="27" cm="1">
         <f t="array" ref="K51">SUM(K7:K50)</f>
         <v>0</v>
       </c>
-      <c r="L51" s="28" cm="1">
+      <c r="L51" s="26" cm="1">
         <f t="array" ref="L51">SUM(L7:L50)</f>
         <v>0</v>
       </c>
-      <c r="M51" s="30" cm="1">
+      <c r="M51" s="28" cm="1">
         <f t="array" ref="M51">SUM(M7:M50)</f>
         <v>0</v>
       </c>
-      <c r="N51" s="31" cm="1">
+      <c r="N51" s="29" cm="1">
         <f t="array" ref="N51">SUM(G51+I51+K51+M51)</f>
         <v>0</v>
       </c>
       <c r="O51" s="6"/>
       <c r="P51" s="6"/>
-      <c r="Q51" s="7"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="7"/>
-      <c r="T51" s="7"/>
-      <c r="U51" s="7"/>
-      <c r="V51" s="7"/>
-      <c r="W51" s="7"/>
     </row>
     <row r="52" ht="21.85" customHeight="1">
-      <c r="A52" s="27"/>
+      <c r="A52" s="25"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
-      <c r="D52" t="s" s="12">
+      <c r="D52" t="s" s="11">
         <v>19</v>
       </c>
       <c r="E52" s="6"/>
@@ -2925,113 +2553,85 @@
       <c r="I52" s="6"/>
       <c r="J52" s="6"/>
       <c r="K52" s="6"/>
-      <c r="L52" s="10"/>
-      <c r="M52" s="14"/>
+      <c r="L52" s="9"/>
+      <c r="M52" s="13"/>
       <c r="N52" s="6"/>
       <c r="O52" s="6"/>
       <c r="P52" s="6"/>
-      <c r="Q52" s="7"/>
-      <c r="R52" s="7"/>
-      <c r="S52" s="7"/>
-      <c r="T52" s="7"/>
-      <c r="U52" s="7"/>
-      <c r="V52" s="7"/>
-      <c r="W52" s="7"/>
     </row>
     <row r="53" ht="21.85" customHeight="1">
-      <c r="A53" s="27"/>
-      <c r="B53" s="32"/>
-      <c r="C53" s="33"/>
-      <c r="D53" t="s" s="12">
+      <c r="A53" s="25"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="31"/>
+      <c r="D53" t="s" s="11">
         <v>20</v>
       </c>
-      <c r="E53" s="7"/>
-      <c r="F53" s="33"/>
-      <c r="G53" s="33"/>
-      <c r="H53" s="33"/>
-      <c r="I53" s="34"/>
-      <c r="J53" s="33"/>
-      <c r="K53" s="34"/>
-      <c r="L53" s="33"/>
-      <c r="M53" s="35"/>
-      <c r="N53" s="36"/>
-      <c r="O53" t="s" s="10">
+      <c r="E53" s="32"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="31"/>
+      <c r="H53" s="31"/>
+      <c r="I53" s="33"/>
+      <c r="J53" s="31"/>
+      <c r="K53" s="33"/>
+      <c r="L53" s="31"/>
+      <c r="M53" s="34"/>
+      <c r="N53" s="35"/>
+      <c r="O53" t="s" s="9">
         <v>21</v>
       </c>
-      <c r="P53" s="37" cm="1">
+      <c r="P53" s="36" cm="1">
         <f t="array" ref="P53">SUM(F51,J51,L51)+H51</f>
         <v>0</v>
       </c>
-      <c r="Q53" s="7"/>
-      <c r="R53" s="7"/>
-      <c r="S53" s="7"/>
-      <c r="T53" s="7"/>
-      <c r="U53" s="7"/>
-      <c r="V53" s="7"/>
-      <c r="W53" s="7"/>
     </row>
     <row r="54" ht="21.85" customHeight="1">
-      <c r="A54" s="27"/>
-      <c r="B54" s="32"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="33"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="33"/>
-      <c r="G54" s="33"/>
-      <c r="H54" s="33"/>
-      <c r="I54" s="34"/>
-      <c r="J54" s="33"/>
-      <c r="K54" s="34"/>
-      <c r="L54" s="33"/>
-      <c r="M54" s="35"/>
-      <c r="N54" s="36"/>
-      <c r="O54" t="s" s="10">
+      <c r="A54" s="25"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="31"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="31"/>
+      <c r="G54" s="31"/>
+      <c r="H54" s="31"/>
+      <c r="I54" s="33"/>
+      <c r="J54" s="31"/>
+      <c r="K54" s="33"/>
+      <c r="L54" s="31"/>
+      <c r="M54" s="34"/>
+      <c r="N54" s="35"/>
+      <c r="O54" t="s" s="9">
         <v>22</v>
       </c>
-      <c r="P54" s="37" cm="1">
+      <c r="P54" s="36" cm="1">
         <f t="array" ref="P54">SUM(G51+K51+M51)</f>
         <v>0</v>
       </c>
-      <c r="Q54" s="7"/>
-      <c r="R54" s="7"/>
-      <c r="S54" s="7"/>
-      <c r="T54" s="7"/>
-      <c r="U54" s="7"/>
-      <c r="V54" s="7"/>
-      <c r="W54" s="7"/>
     </row>
     <row r="55" ht="148.75" customHeight="1">
-      <c r="A55" t="s" s="38">
+      <c r="A55" t="s" s="37">
         <v>23</v>
       </c>
-      <c r="B55" s="39"/>
-      <c r="C55" s="40"/>
-      <c r="D55" t="s" s="41">
+      <c r="B55" s="38"/>
+      <c r="C55" s="39"/>
+      <c r="D55" t="s" s="40">
         <v>24</v>
       </c>
-      <c r="E55" t="s" s="42">
+      <c r="E55" t="s" s="41">
         <v>25</v>
       </c>
-      <c r="F55" s="43"/>
-      <c r="G55" s="44"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="27"/>
-      <c r="J55" t="s" s="45">
+      <c r="F55" s="42"/>
+      <c r="G55" s="43"/>
+      <c r="H55" s="25"/>
+      <c r="I55" s="25"/>
+      <c r="J55" t="s" s="44">
         <v>26</v>
       </c>
-      <c r="K55" s="27"/>
-      <c r="L55" s="27"/>
-      <c r="M55" s="46"/>
-      <c r="N55" s="27"/>
-      <c r="O55" s="27"/>
-      <c r="P55" s="27"/>
-      <c r="Q55" s="7"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="7"/>
-      <c r="T55" s="7"/>
-      <c r="U55" s="7"/>
-      <c r="V55" s="7"/>
-      <c r="W55" s="7"/>
+      <c r="K55" s="25"/>
+      <c r="L55" s="25"/>
+      <c r="M55" s="45"/>
+      <c r="N55" s="25"/>
+      <c r="O55" s="25"/>
+      <c r="P55" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="13">

--- a/template.xlsx
+++ b/template.xlsx
@@ -1,17 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vanbestco-my.sharepoint.com/personal/james_lin_vanbestco_com/Documents/桌面/Files/Others/Business Trip/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_2C758F117E5E30E5FC84F013E7303124525A7711" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91DDA741-9524-8E47-B0E0-F07268635D1A}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="22240" windowHeight="17960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId5"/>
+    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -33,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>出差旅費報告表</t>
   </si>
@@ -46,6 +68,8 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
       </rPr>
       <t>出差事由：</t>
     </r>
@@ -116,6 +140,8 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
       </rPr>
       <t>預支</t>
     </r>
@@ -124,6 +150,8 @@
         <sz val="12"/>
         <color indexed="10"/>
         <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -135,6 +163,8 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
       </rPr>
       <t>繳回公司</t>
     </r>
@@ -143,6 +173,8 @@
         <sz val="12"/>
         <color indexed="10"/>
         <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -154,6 +186,8 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
       </rPr>
       <t xml:space="preserve">公司應付
 </t>
@@ -163,6 +197,8 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -175,13 +211,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="59" formatCode="&quot; &quot;* #,##0.00&quot; &quot;;&quot;-&quot;* #,##0.00&quot; &quot;;&quot; &quot;* &quot;-&quot;??&quot; &quot;"/>
-    <numFmt numFmtId="60" formatCode="mm/dd"/>
-    <numFmt numFmtId="61" formatCode="#,##0&quot; &quot;"/>
-    <numFmt numFmtId="62" formatCode="#,##0&quot; &quot;;(#,##0)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="&quot; &quot;* #,##0.00&quot; &quot;;&quot;-&quot;* #,##0.00&quot; &quot;;&quot; &quot;* &quot;-&quot;??&quot; &quot;"/>
+    <numFmt numFmtId="177" formatCode="mm/dd"/>
+    <numFmt numFmtId="178" formatCode="#,##0&quot; &quot;"/>
+    <numFmt numFmtId="179" formatCode="#,##0&quot; &quot;;\(#,##0\)"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -190,29 +225,38 @@
       <name val="新細明體"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <sz val="15"/>
       <color indexed="8"/>
       <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="10"/>
       <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
     </font>
     <font>
       <sz val="13"/>
       <color indexed="8"/>
       <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Wawati TC"/>
+      <family val="3"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="5">
@@ -329,184 +373,235 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+  <cellXfs count="47">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="177" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="59" fontId="3" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="59" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="60" fontId="5" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="61" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="62" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="61" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="62" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="4" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="61" fontId="4" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="62" fontId="4" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="59" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
+    <xf numFmtId="178" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
       <font>
-        <color rgb="ffff0000"/>
+        <color rgb="FFFF0000"/>
       </font>
     </dxf>
   </dxfs>
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ff0000d4"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ffccffcc"/>
-      <rgbColor rgb="ffffff99"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FF0000D4"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -708,7 +803,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -726,7 +821,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -755,7 +850,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -780,7 +875,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -805,7 +900,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -830,7 +925,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -855,7 +950,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -880,7 +975,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -905,7 +1000,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -930,7 +1025,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -955,7 +1050,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -968,9 +1063,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -987,7 +1088,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1005,7 +1106,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1030,7 +1131,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1055,7 +1156,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1080,7 +1181,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1105,7 +1206,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1130,7 +1231,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1155,7 +1256,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1180,7 +1281,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1205,7 +1306,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1230,7 +1331,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1243,9 +1344,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1259,7 +1366,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1277,7 +1384,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1306,7 +1413,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1331,7 +1438,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1356,7 +1463,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1381,7 +1488,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1406,7 +1513,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1431,7 +1538,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1456,7 +1563,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1481,7 +1588,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1506,7 +1613,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1519,1126 +1626,1205 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P55"/>
-  <sheetFormatPr defaultColWidth="10.8333" defaultRowHeight="14" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P59"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.8516" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="7" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.8516" style="1" customWidth="1"/>
-    <col min="4" max="4" width="33.3516" style="1" customWidth="1"/>
-    <col min="5" max="16" width="10.8516" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="10.8516" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="33.33203125" style="1" customWidth="1"/>
+    <col min="5" max="17" width="10.83203125" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30.6" customHeight="1">
-      <c r="A1" t="s" s="2">
+    <row r="1" spans="1:16" ht="30.5" customHeight="1">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-    </row>
-    <row r="2" ht="30.6" customHeight="1">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-    </row>
-    <row r="3" ht="21.85" customHeight="1">
-      <c r="A3" t="s" s="9">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+    </row>
+    <row r="2" spans="1:16" ht="30.5" customHeight="1">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+    </row>
+    <row r="3" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="6"/>
-      <c r="D3" t="s" s="9">
+      <c r="B3" s="6"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" t="s" s="11">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="12"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-    </row>
-    <row r="4" ht="21.85" customHeight="1">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-    </row>
-    <row r="5" ht="21.85" customHeight="1">
-      <c r="A5" t="s" s="14">
+      <c r="K3" s="8"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+    </row>
+    <row r="4" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+    </row>
+    <row r="5" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A5" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s" s="14">
+      <c r="B5" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C5" t="s" s="14">
+      <c r="C5" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="D5" t="s" s="14">
+      <c r="D5" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="E5" t="s" s="14">
+      <c r="E5" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="F5" t="s" s="15">
+      <c r="F5" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="16"/>
-      <c r="H5" t="s" s="15">
+      <c r="G5" s="33"/>
+      <c r="H5" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="16"/>
-      <c r="J5" t="s" s="15">
+      <c r="I5" s="33"/>
+      <c r="J5" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="16"/>
-      <c r="L5" t="s" s="15">
+      <c r="K5" s="33"/>
+      <c r="L5" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="M5" s="16"/>
-      <c r="N5" t="s" s="17">
+      <c r="M5" s="33"/>
+      <c r="N5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O5" t="s" s="15">
+      <c r="O5" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="P5" s="16"/>
-    </row>
-    <row r="6" ht="21.85" customHeight="1">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" t="s" s="17">
+      <c r="P5" s="33"/>
+    </row>
+    <row r="6" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A6" s="45"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G6" t="s" s="17">
+      <c r="G6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H6" t="s" s="17">
+      <c r="H6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I6" t="s" s="17">
+      <c r="I6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="J6" t="s" s="17">
+      <c r="J6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="K6" t="s" s="17">
+      <c r="K6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="L6" t="s" s="17">
+      <c r="L6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="M6" t="s" s="17">
+      <c r="M6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="N6" t="s" s="17">
+      <c r="N6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="O6" t="s" s="17">
+      <c r="O6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="P6" t="s" s="17">
+      <c r="P6" s="10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" ht="21.85" customHeight="1">
-      <c r="A7" s="19"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="17"/>
-    </row>
-    <row r="8" ht="21.85" customHeight="1">
-      <c r="A8" s="19"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="17"/>
-    </row>
-    <row r="9" ht="21.85" customHeight="1">
-      <c r="A9" s="19"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="24"/>
-      <c r="P9" s="17"/>
-    </row>
-    <row r="10" ht="21.85" customHeight="1">
-      <c r="A10" s="19"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="17"/>
-    </row>
-    <row r="11" ht="21.85" customHeight="1">
-      <c r="A11" s="19"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="17"/>
-    </row>
-    <row r="12" ht="21.85" customHeight="1">
-      <c r="A12" s="19"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="17"/>
-    </row>
-    <row r="13" ht="21.85" customHeight="1">
-      <c r="A13" s="19"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="17"/>
-    </row>
-    <row r="14" ht="21.85" customHeight="1">
-      <c r="A14" s="19"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="17"/>
-    </row>
-    <row r="15" ht="21.85" customHeight="1">
-      <c r="A15" s="19"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="17"/>
-    </row>
-    <row r="16" ht="21.85" customHeight="1">
-      <c r="A16" s="19"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="17"/>
-    </row>
-    <row r="17" ht="21.85" customHeight="1">
-      <c r="A17" s="19"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="17"/>
-    </row>
-    <row r="18" ht="21.85" customHeight="1">
-      <c r="A18" s="19"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="24"/>
-      <c r="P18" s="17"/>
-    </row>
-    <row r="19" ht="21.85" customHeight="1">
-      <c r="A19" s="19"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="22"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="17"/>
-    </row>
-    <row r="20" ht="21.85" customHeight="1">
-      <c r="A20" s="19"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="22"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="17"/>
-    </row>
-    <row r="21" ht="21.85" customHeight="1">
-      <c r="A21" s="19"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="22"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="17"/>
-    </row>
-    <row r="22" ht="21.85" customHeight="1">
-      <c r="A22" s="19"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="17"/>
-    </row>
-    <row r="23" ht="21.85" customHeight="1">
-      <c r="A23" s="19"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="23"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="17"/>
-    </row>
-    <row r="24" ht="21.85" customHeight="1">
-      <c r="A24" s="19"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="22"/>
-      <c r="N24" s="23"/>
-      <c r="O24" s="24"/>
-      <c r="P24" s="17"/>
-    </row>
-    <row r="25" ht="21.85" customHeight="1">
-      <c r="A25" s="19"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="22"/>
-      <c r="N25" s="23"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="17"/>
-    </row>
-    <row r="26" ht="21.85" customHeight="1">
-      <c r="A26" s="19"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="22"/>
-      <c r="N26" s="23"/>
-      <c r="O26" s="24"/>
-      <c r="P26" s="17"/>
-    </row>
-    <row r="27" ht="21.85" customHeight="1">
-      <c r="A27" s="19"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="21"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="22"/>
-      <c r="N27" s="23"/>
-      <c r="O27" s="24"/>
-      <c r="P27" s="17"/>
-    </row>
-    <row r="28" ht="21.85" customHeight="1">
-      <c r="A28" s="19"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="23"/>
-      <c r="O28" s="24"/>
-      <c r="P28" s="17"/>
-    </row>
-    <row r="29" ht="21.85" customHeight="1">
-      <c r="A29" s="19"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="22"/>
-      <c r="N29" s="23"/>
-      <c r="O29" s="24"/>
-      <c r="P29" s="17"/>
-    </row>
-    <row r="30" ht="21.85" customHeight="1">
-      <c r="A30" s="19"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="22"/>
-      <c r="N30" s="23"/>
-      <c r="O30" s="24"/>
-      <c r="P30" s="17"/>
-    </row>
-    <row r="31" ht="21.85" customHeight="1">
-      <c r="A31" s="19"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="22"/>
-      <c r="N31" s="23"/>
-      <c r="O31" s="24"/>
-      <c r="P31" s="17"/>
-    </row>
-    <row r="32" ht="21.85" customHeight="1">
-      <c r="A32" s="19"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="21"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="22"/>
-      <c r="N32" s="23"/>
-      <c r="O32" s="24"/>
-      <c r="P32" s="17"/>
-    </row>
-    <row r="33" ht="21.85" customHeight="1">
-      <c r="A33" s="19"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="22"/>
-      <c r="N33" s="23"/>
-      <c r="O33" s="24"/>
-      <c r="P33" s="17"/>
-    </row>
-    <row r="34" ht="21.85" customHeight="1">
-      <c r="A34" s="19"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="21"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="22"/>
-      <c r="N34" s="23"/>
-      <c r="O34" s="24"/>
-      <c r="P34" s="17"/>
-    </row>
-    <row r="35" ht="21.85" customHeight="1">
-      <c r="A35" s="19"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="21"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="22"/>
-      <c r="N35" s="23"/>
-      <c r="O35" s="24"/>
-      <c r="P35" s="17"/>
-    </row>
-    <row r="36" ht="21.85" customHeight="1">
-      <c r="A36" s="19"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="22"/>
-      <c r="N36" s="23"/>
-      <c r="O36" s="24"/>
-      <c r="P36" s="17"/>
-    </row>
-    <row r="37" ht="21.85" customHeight="1">
-      <c r="A37" s="19"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="21"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="21"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="22"/>
-      <c r="N37" s="23"/>
-      <c r="O37" s="24"/>
-      <c r="P37" s="17"/>
-    </row>
-    <row r="38" ht="21.85" customHeight="1">
-      <c r="A38" s="19"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="21"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="21"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="22"/>
-      <c r="N38" s="23"/>
-      <c r="O38" s="24"/>
-      <c r="P38" s="17"/>
-    </row>
-    <row r="39" ht="21.85" customHeight="1">
-      <c r="A39" s="19"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="22"/>
-      <c r="N39" s="23"/>
-      <c r="O39" s="24"/>
-      <c r="P39" s="17"/>
-    </row>
-    <row r="40" ht="21.85" customHeight="1">
-      <c r="A40" s="19"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="22"/>
-      <c r="N40" s="23"/>
-      <c r="O40" s="24"/>
-      <c r="P40" s="17"/>
-    </row>
-    <row r="41" ht="21.85" customHeight="1">
-      <c r="A41" s="19"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="21"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="22"/>
-      <c r="N41" s="23"/>
-      <c r="O41" s="24"/>
-      <c r="P41" s="17"/>
-    </row>
-    <row r="42" ht="21.85" customHeight="1">
-      <c r="A42" s="19"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="21"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="21"/>
-      <c r="L42" s="6"/>
-      <c r="M42" s="22"/>
-      <c r="N42" s="23"/>
-      <c r="O42" s="24"/>
-      <c r="P42" s="17"/>
-    </row>
-    <row r="43" ht="21.85" customHeight="1">
-      <c r="A43" s="19"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="21"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="21"/>
-      <c r="L43" s="6"/>
-      <c r="M43" s="22"/>
-      <c r="N43" s="23"/>
-      <c r="O43" s="24"/>
-      <c r="P43" s="17"/>
-    </row>
-    <row r="44" ht="21.85" customHeight="1">
-      <c r="A44" s="19"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="21"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="21"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="22"/>
-      <c r="N44" s="23"/>
-      <c r="O44" s="24"/>
-      <c r="P44" s="17"/>
-    </row>
-    <row r="45" ht="21.85" customHeight="1">
-      <c r="A45" s="19"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="21"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="21"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="22"/>
-      <c r="N45" s="23"/>
-      <c r="O45" s="24"/>
-      <c r="P45" s="17"/>
-    </row>
-    <row r="46" ht="21.85" customHeight="1">
-      <c r="A46" s="19"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="21"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="21"/>
-      <c r="L46" s="6"/>
-      <c r="M46" s="22"/>
-      <c r="N46" s="23"/>
-      <c r="O46" s="24"/>
-      <c r="P46" s="17"/>
-    </row>
-    <row r="47" ht="21.85" customHeight="1">
-      <c r="A47" s="19"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="21"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="21"/>
-      <c r="L47" s="6"/>
-      <c r="M47" s="22"/>
-      <c r="N47" s="23"/>
-      <c r="O47" s="24"/>
-      <c r="P47" s="17"/>
-    </row>
-    <row r="48" ht="21.85" customHeight="1">
-      <c r="A48" s="19"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="21"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="21"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="22"/>
-      <c r="N48" s="23"/>
-      <c r="O48" s="24"/>
-      <c r="P48" s="17"/>
-    </row>
-    <row r="49" ht="21.85" customHeight="1">
-      <c r="A49" s="19"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="21"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="21"/>
-      <c r="L49" s="6"/>
-      <c r="M49" s="22"/>
-      <c r="N49" s="23"/>
-      <c r="O49" s="24"/>
-      <c r="P49" s="17"/>
-    </row>
-    <row r="50" ht="21.85" customHeight="1">
-      <c r="A50" s="19"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="21"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="21"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="22"/>
-      <c r="N50" s="23"/>
-      <c r="O50" s="24"/>
-      <c r="P50" s="17"/>
-    </row>
-    <row r="51" ht="21.85" customHeight="1">
-      <c r="A51" s="25"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="26" cm="1">
-        <f t="array" ref="F51">SUM(F7:F50)</f>
+    <row r="7" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A7" s="11"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="10"/>
+    </row>
+    <row r="8" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A8" s="11"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="10"/>
+    </row>
+    <row r="9" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A9" s="11"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="10"/>
+    </row>
+    <row r="10" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A10" s="11"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="10"/>
+    </row>
+    <row r="11" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A11" s="11"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="10"/>
+    </row>
+    <row r="12" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A12" s="11"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="10"/>
+    </row>
+    <row r="13" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A13" s="11"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="10"/>
+    </row>
+    <row r="14" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A14" s="11"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="10"/>
+    </row>
+    <row r="15" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A15" s="11"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="10"/>
+    </row>
+    <row r="16" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A16" s="11"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="10"/>
+    </row>
+    <row r="17" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A17" s="11"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="10"/>
+    </row>
+    <row r="18" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A18" s="11"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="10"/>
+    </row>
+    <row r="19" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A19" s="11"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="10"/>
+    </row>
+    <row r="20" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A20" s="11"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="10"/>
+    </row>
+    <row r="21" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A21" s="11"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="10"/>
+    </row>
+    <row r="22" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A22" s="11"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="10"/>
+    </row>
+    <row r="23" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A23" s="11"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="16"/>
+      <c r="P23" s="10"/>
+    </row>
+    <row r="24" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A24" s="11"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="16"/>
+      <c r="P24" s="10"/>
+    </row>
+    <row r="25" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A25" s="11"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="16"/>
+      <c r="P25" s="10"/>
+    </row>
+    <row r="26" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A26" s="11"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="16"/>
+      <c r="P26" s="10"/>
+    </row>
+    <row r="27" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A27" s="11"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="16"/>
+      <c r="P27" s="10"/>
+    </row>
+    <row r="28" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A28" s="11"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="16"/>
+      <c r="P28" s="10"/>
+    </row>
+    <row r="29" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A29" s="11"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="16"/>
+      <c r="P29" s="10"/>
+    </row>
+    <row r="30" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A30" s="11"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="16"/>
+      <c r="P30" s="10"/>
+    </row>
+    <row r="31" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A31" s="11"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="16"/>
+      <c r="P31" s="10"/>
+    </row>
+    <row r="32" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A32" s="11"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="16"/>
+      <c r="P32" s="10"/>
+    </row>
+    <row r="33" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A33" s="11"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="16"/>
+      <c r="P33" s="10"/>
+    </row>
+    <row r="34" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A34" s="11"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="15"/>
+      <c r="O34" s="16"/>
+      <c r="P34" s="10"/>
+    </row>
+    <row r="35" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A35" s="11"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="16"/>
+      <c r="P35" s="10"/>
+    </row>
+    <row r="36" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A36" s="11"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="16"/>
+      <c r="P36" s="10"/>
+    </row>
+    <row r="37" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A37" s="11"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="15"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="10"/>
+    </row>
+    <row r="38" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A38" s="11"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="16"/>
+      <c r="P38" s="10"/>
+    </row>
+    <row r="39" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A39" s="11"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="14"/>
+      <c r="N39" s="15"/>
+      <c r="O39" s="16"/>
+      <c r="P39" s="10"/>
+    </row>
+    <row r="40" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A40" s="11"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="14"/>
+      <c r="N40" s="15"/>
+      <c r="O40" s="16"/>
+      <c r="P40" s="10"/>
+    </row>
+    <row r="41" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A41" s="11"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="14"/>
+      <c r="N41" s="15"/>
+      <c r="O41" s="16"/>
+      <c r="P41" s="10"/>
+    </row>
+    <row r="42" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A42" s="11"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="14"/>
+      <c r="N42" s="15"/>
+      <c r="O42" s="16"/>
+      <c r="P42" s="10"/>
+    </row>
+    <row r="43" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A43" s="11"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="13"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="14"/>
+      <c r="N43" s="15"/>
+      <c r="O43" s="16"/>
+      <c r="P43" s="10"/>
+    </row>
+    <row r="44" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A44" s="11"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="13"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="14"/>
+      <c r="N44" s="15"/>
+      <c r="O44" s="16"/>
+      <c r="P44" s="10"/>
+    </row>
+    <row r="45" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A45" s="11"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="13"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="14"/>
+      <c r="N45" s="15"/>
+      <c r="O45" s="16"/>
+      <c r="P45" s="10"/>
+    </row>
+    <row r="46" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A46" s="11"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="13"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="14"/>
+      <c r="N46" s="15"/>
+      <c r="O46" s="16"/>
+      <c r="P46" s="10"/>
+    </row>
+    <row r="47" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A47" s="11"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="13"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="14"/>
+      <c r="N47" s="15"/>
+      <c r="O47" s="16"/>
+      <c r="P47" s="10"/>
+    </row>
+    <row r="48" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A48" s="11"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="13"/>
+      <c r="L48" s="2"/>
+      <c r="M48" s="14"/>
+      <c r="N48" s="15"/>
+      <c r="O48" s="16"/>
+      <c r="P48" s="10"/>
+    </row>
+    <row r="49" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A49" s="11"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="13"/>
+      <c r="L49" s="2"/>
+      <c r="M49" s="14"/>
+      <c r="N49" s="15"/>
+      <c r="O49" s="16"/>
+      <c r="P49" s="10"/>
+    </row>
+    <row r="50" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A50" s="11"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="13"/>
+      <c r="L50" s="2"/>
+      <c r="M50" s="14"/>
+      <c r="N50" s="15"/>
+      <c r="O50" s="16"/>
+      <c r="P50" s="10"/>
+    </row>
+    <row r="51" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A51" s="11"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="14"/>
+      <c r="N51" s="15"/>
+      <c r="O51" s="16"/>
+      <c r="P51" s="10"/>
+    </row>
+    <row r="52" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A52" s="11"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="13"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="14"/>
+      <c r="N52" s="15"/>
+      <c r="O52" s="16"/>
+      <c r="P52" s="10"/>
+    </row>
+    <row r="53" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A53" s="11"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="13"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="2"/>
+      <c r="M53" s="14"/>
+      <c r="N53" s="15"/>
+      <c r="O53" s="16"/>
+      <c r="P53" s="10"/>
+    </row>
+    <row r="54" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A54" s="11"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="2"/>
+      <c r="M54" s="14"/>
+      <c r="N54" s="15"/>
+      <c r="O54" s="16"/>
+      <c r="P54" s="10"/>
+    </row>
+    <row r="55" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A55" s="17"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="18" cm="1">
+        <f t="array" ref="F55">SUM(F7:F54)</f>
         <v>0</v>
       </c>
-      <c r="G51" s="27" cm="1">
-        <f t="array" ref="G51">SUM(G7:G50)</f>
+      <c r="G55" s="19" cm="1">
+        <f t="array" ref="G55">SUM(G7:G54)</f>
         <v>0</v>
       </c>
-      <c r="H51" s="21" cm="1">
-        <f t="array" ref="H51">SUM(H7:H50)</f>
+      <c r="H55" s="13" cm="1">
+        <f t="array" ref="H55">SUM(H7:H54)</f>
         <v>0</v>
       </c>
-      <c r="I51" s="27" cm="1">
-        <f t="array" ref="I51">SUM(I7:I50)</f>
+      <c r="I55" s="19" cm="1">
+        <f t="array" ref="I55">SUM(I7:I54)</f>
         <v>0</v>
       </c>
-      <c r="J51" s="21" cm="1">
-        <f t="array" ref="J51">SUM(J7:J50)</f>
+      <c r="J55" s="13" cm="1">
+        <f t="array" ref="J55">SUM(J7:J54)</f>
         <v>0</v>
       </c>
-      <c r="K51" s="27" cm="1">
-        <f t="array" ref="K51">SUM(K7:K50)</f>
+      <c r="K55" s="19" cm="1">
+        <f t="array" ref="K55">SUM(K7:K54)</f>
         <v>0</v>
       </c>
-      <c r="L51" s="26" cm="1">
-        <f t="array" ref="L51">SUM(L7:L50)</f>
+      <c r="L55" s="18" cm="1">
+        <f t="array" ref="L55">SUM(L7:L54)</f>
         <v>0</v>
       </c>
-      <c r="M51" s="28" cm="1">
-        <f t="array" ref="M51">SUM(M7:M50)</f>
+      <c r="M55" s="20" cm="1">
+        <f t="array" ref="M55">SUM(M7:M54)</f>
         <v>0</v>
       </c>
-      <c r="N51" s="29" cm="1">
-        <f t="array" ref="N51">SUM(G51+I51+K51+M51)</f>
+      <c r="N55" s="21" cm="1">
+        <f t="array" ref="N55">SUM(G55+I55+K55+M55)</f>
         <v>0</v>
       </c>
-      <c r="O51" s="6"/>
-      <c r="P51" s="6"/>
-    </row>
-    <row r="52" ht="21.85" customHeight="1">
-      <c r="A52" s="25"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" t="s" s="11">
+      <c r="O55" s="2"/>
+      <c r="P55" s="2"/>
+    </row>
+    <row r="56" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A56" s="17"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="9"/>
-      <c r="M52" s="13"/>
-      <c r="N52" s="6"/>
-      <c r="O52" s="6"/>
-      <c r="P52" s="6"/>
-    </row>
-    <row r="53" ht="21.85" customHeight="1">
-      <c r="A53" s="25"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="31"/>
-      <c r="D53" t="s" s="11">
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="5"/>
+      <c r="M56" s="9"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="2"/>
+    </row>
+    <row r="57" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A57" s="17"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E53" s="32"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
-      <c r="H53" s="31"/>
-      <c r="I53" s="33"/>
-      <c r="J53" s="31"/>
-      <c r="K53" s="33"/>
-      <c r="L53" s="31"/>
-      <c r="M53" s="34"/>
-      <c r="N53" s="35"/>
-      <c r="O53" t="s" s="9">
+      <c r="E57" s="24"/>
+      <c r="F57" s="23"/>
+      <c r="G57" s="23"/>
+      <c r="H57" s="23"/>
+      <c r="I57" s="25"/>
+      <c r="J57" s="23"/>
+      <c r="K57" s="25"/>
+      <c r="L57" s="23"/>
+      <c r="M57" s="26"/>
+      <c r="N57" s="27"/>
+      <c r="O57" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="P53" s="36" cm="1">
-        <f t="array" ref="P53">SUM(F51,J51,L51)+H51</f>
+      <c r="P57" s="28" cm="1">
+        <f t="array" ref="P57">SUM(F55,J55,L55)+H55</f>
         <v>0</v>
       </c>
     </row>
-    <row r="54" ht="21.85" customHeight="1">
-      <c r="A54" s="25"/>
-      <c r="B54" s="30"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="32"/>
-      <c r="F54" s="31"/>
-      <c r="G54" s="31"/>
-      <c r="H54" s="31"/>
-      <c r="I54" s="33"/>
-      <c r="J54" s="31"/>
-      <c r="K54" s="33"/>
-      <c r="L54" s="31"/>
-      <c r="M54" s="34"/>
-      <c r="N54" s="35"/>
-      <c r="O54" t="s" s="9">
+    <row r="58" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A58" s="17"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="23"/>
+      <c r="D58" s="23"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="23"/>
+      <c r="G58" s="23"/>
+      <c r="H58" s="23"/>
+      <c r="I58" s="25"/>
+      <c r="J58" s="23"/>
+      <c r="K58" s="25"/>
+      <c r="L58" s="23"/>
+      <c r="M58" s="26"/>
+      <c r="N58" s="27"/>
+      <c r="O58" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="P54" s="36" cm="1">
-        <f t="array" ref="P54">SUM(G51+K51+M51)</f>
+      <c r="P58" s="46">
+        <f>SUM(G55+K55+M55+I55)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="55" ht="148.75" customHeight="1">
-      <c r="A55" t="s" s="37">
+    <row r="59" spans="1:16" ht="148.75" customHeight="1">
+      <c r="A59" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B55" s="38"/>
-      <c r="C55" s="39"/>
-      <c r="D55" t="s" s="40">
+      <c r="B59" s="35"/>
+      <c r="C59" s="36"/>
+      <c r="D59" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="E55" t="s" s="41">
+      <c r="E59" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="F55" s="42"/>
-      <c r="G55" s="43"/>
-      <c r="H55" s="25"/>
-      <c r="I55" s="25"/>
-      <c r="J55" t="s" s="44">
+      <c r="F59" s="38"/>
+      <c r="G59" s="39"/>
+      <c r="H59" s="17"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="K55" s="25"/>
-      <c r="L55" s="25"/>
-      <c r="M55" s="45"/>
-      <c r="N55" s="25"/>
-      <c r="O55" s="25"/>
-      <c r="P55" s="25"/>
+      <c r="K59" s="17"/>
+      <c r="L59" s="17"/>
+      <c r="M59" s="31"/>
+      <c r="N59" s="17"/>
+      <c r="O59" s="17"/>
+      <c r="P59" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="O5:P5"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="E59:G59"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
@@ -2649,13 +2835,14 @@
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="J5:K5"/>
   </mergeCells>
-  <conditionalFormatting sqref="M7:M51 M53:M54">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan" stopIfTrue="1">
+  <phoneticPr fontId="5" type="noConversion"/>
+  <conditionalFormatting sqref="M57:M58 M7:M55">
+    <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="landscape" pageOrder="downThenOver"/>
+  <pageSetup orientation="landscape"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/template.xlsx
+++ b/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vanbestco-my.sharepoint.com/personal/james_lin_vanbestco_com/Documents/桌面/Files/Others/Business Trip/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_2C758F117E5E30E5FC84F013E7303124525A7711" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91DDA741-9524-8E47-B0E0-F07268635D1A}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_2C758F117E5E30E5FC84F013E7303124525A7711" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFA78FD9-5C7D-9B42-AE0B-914ECFE69E07}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="22240" windowHeight="17960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10720" yWindow="1640" windowWidth="22240" windowHeight="17960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -466,6 +466,9 @@
     <xf numFmtId="176" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -504,9 +507,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1645,7 +1645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P59"/>
+  <dimension ref="A1:P65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1" customWidth="1"/>
@@ -1657,22 +1657,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="30.5" customHeight="1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="43"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="44"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
@@ -1737,51 +1737,51 @@
       <c r="P4" s="2"/>
     </row>
     <row r="5" spans="1:16" ht="21.75" customHeight="1">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="44" t="s">
+      <c r="B5" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="33"/>
-      <c r="H5" s="32" t="s">
+      <c r="G5" s="34"/>
+      <c r="H5" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="33"/>
-      <c r="J5" s="32" t="s">
+      <c r="I5" s="34"/>
+      <c r="J5" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="33"/>
-      <c r="L5" s="32" t="s">
+      <c r="K5" s="34"/>
+      <c r="L5" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="M5" s="33"/>
+      <c r="M5" s="34"/>
       <c r="N5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O5" s="32" t="s">
+      <c r="O5" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="P5" s="33"/>
+      <c r="P5" s="34"/>
     </row>
     <row r="6" spans="1:16" ht="21.75" customHeight="1">
-      <c r="A6" s="45"/>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
+      <c r="A6" s="46"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
       <c r="F6" s="10" t="s">
         <v>15</v>
       </c>
@@ -2681,150 +2681,258 @@
       <c r="P54" s="10"/>
     </row>
     <row r="55" spans="1:16" ht="21.75" customHeight="1">
-      <c r="A55" s="17"/>
+      <c r="A55" s="11"/>
       <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="18" cm="1">
-        <f t="array" ref="F55">SUM(F7:F54)</f>
-        <v>0</v>
-      </c>
-      <c r="G55" s="19" cm="1">
-        <f t="array" ref="G55">SUM(G7:G54)</f>
-        <v>0</v>
-      </c>
-      <c r="H55" s="13" cm="1">
-        <f t="array" ref="H55">SUM(H7:H54)</f>
-        <v>0</v>
-      </c>
-      <c r="I55" s="19" cm="1">
-        <f t="array" ref="I55">SUM(I7:I54)</f>
-        <v>0</v>
-      </c>
-      <c r="J55" s="13" cm="1">
-        <f t="array" ref="J55">SUM(J7:J54)</f>
-        <v>0</v>
-      </c>
-      <c r="K55" s="19" cm="1">
-        <f t="array" ref="K55">SUM(K7:K54)</f>
-        <v>0</v>
-      </c>
-      <c r="L55" s="18" cm="1">
-        <f t="array" ref="L55">SUM(L7:L54)</f>
-        <v>0</v>
-      </c>
-      <c r="M55" s="20" cm="1">
-        <f t="array" ref="M55">SUM(M7:M54)</f>
-        <v>0</v>
-      </c>
-      <c r="N55" s="21" cm="1">
-        <f t="array" ref="N55">SUM(G55+I55+K55+M55)</f>
-        <v>0</v>
-      </c>
-      <c r="O55" s="2"/>
-      <c r="P55" s="2"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="13"/>
+      <c r="L55" s="2"/>
+      <c r="M55" s="14"/>
+      <c r="N55" s="15"/>
+      <c r="O55" s="16"/>
+      <c r="P55" s="10"/>
     </row>
     <row r="56" spans="1:16" ht="21.75" customHeight="1">
-      <c r="A56" s="17"/>
+      <c r="A56" s="11"/>
       <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E56" s="2"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="5"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
+      <c r="I56" s="13"/>
       <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
-      <c r="L56" s="5"/>
-      <c r="M56" s="9"/>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
-      <c r="P56" s="2"/>
+      <c r="K56" s="13"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="14"/>
+      <c r="N56" s="15"/>
+      <c r="O56" s="16"/>
+      <c r="P56" s="10"/>
     </row>
     <row r="57" spans="1:16" ht="21.75" customHeight="1">
-      <c r="A57" s="17"/>
-      <c r="B57" s="22"/>
-      <c r="C57" s="23"/>
-      <c r="D57" s="7" t="s">
+      <c r="A57" s="11"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="13"/>
+      <c r="L57" s="2"/>
+      <c r="M57" s="14"/>
+      <c r="N57" s="15"/>
+      <c r="O57" s="16"/>
+      <c r="P57" s="10"/>
+    </row>
+    <row r="58" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A58" s="11"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="13"/>
+      <c r="L58" s="2"/>
+      <c r="M58" s="14"/>
+      <c r="N58" s="15"/>
+      <c r="O58" s="16"/>
+      <c r="P58" s="10"/>
+    </row>
+    <row r="59" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A59" s="11"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="13"/>
+      <c r="L59" s="2"/>
+      <c r="M59" s="14"/>
+      <c r="N59" s="15"/>
+      <c r="O59" s="16"/>
+      <c r="P59" s="10"/>
+    </row>
+    <row r="60" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A60" s="11"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="13"/>
+      <c r="L60" s="2"/>
+      <c r="M60" s="14"/>
+      <c r="N60" s="15"/>
+      <c r="O60" s="16"/>
+      <c r="P60" s="10"/>
+    </row>
+    <row r="61" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A61" s="17"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="18" cm="1">
+        <f t="array" ref="F61">SUM(F7:F60)</f>
+        <v>0</v>
+      </c>
+      <c r="G61" s="19" cm="1">
+        <f t="array" ref="G61">SUM(G7:G60)</f>
+        <v>0</v>
+      </c>
+      <c r="H61" s="13" cm="1">
+        <f t="array" ref="H61">SUM(H7:H60)</f>
+        <v>0</v>
+      </c>
+      <c r="I61" s="19" cm="1">
+        <f t="array" ref="I61">SUM(I7:I60)</f>
+        <v>0</v>
+      </c>
+      <c r="J61" s="13" cm="1">
+        <f t="array" ref="J61">SUM(J7:J60)</f>
+        <v>0</v>
+      </c>
+      <c r="K61" s="19" cm="1">
+        <f t="array" ref="K61">SUM(K7:K60)</f>
+        <v>0</v>
+      </c>
+      <c r="L61" s="18" cm="1">
+        <f t="array" ref="L61">SUM(L7:L60)</f>
+        <v>0</v>
+      </c>
+      <c r="M61" s="20" cm="1">
+        <f t="array" ref="M61">SUM(M7:M60)</f>
+        <v>0</v>
+      </c>
+      <c r="N61" s="21" cm="1">
+        <f t="array" ref="N61">SUM(G61+I61+K61+M61)</f>
+        <v>0</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" s="2"/>
+    </row>
+    <row r="62" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A62" s="17"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="5"/>
+      <c r="M62" s="9"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" s="2"/>
+    </row>
+    <row r="63" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A63" s="17"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="23"/>
+      <c r="D63" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E57" s="24"/>
-      <c r="F57" s="23"/>
-      <c r="G57" s="23"/>
-      <c r="H57" s="23"/>
-      <c r="I57" s="25"/>
-      <c r="J57" s="23"/>
-      <c r="K57" s="25"/>
-      <c r="L57" s="23"/>
-      <c r="M57" s="26"/>
-      <c r="N57" s="27"/>
-      <c r="O57" s="5" t="s">
+      <c r="E63" s="24"/>
+      <c r="F63" s="23"/>
+      <c r="G63" s="23"/>
+      <c r="H63" s="23"/>
+      <c r="I63" s="25"/>
+      <c r="J63" s="23"/>
+      <c r="K63" s="25"/>
+      <c r="L63" s="23"/>
+      <c r="M63" s="26"/>
+      <c r="N63" s="27"/>
+      <c r="O63" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="P57" s="28" cm="1">
-        <f t="array" ref="P57">SUM(F55,J55,L55)+H55</f>
+      <c r="P63" s="28" cm="1">
+        <f t="array" ref="P63">SUM(F61,J61,L61)+H61</f>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="21.75" customHeight="1">
-      <c r="A58" s="17"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="23"/>
-      <c r="D58" s="23"/>
-      <c r="E58" s="24"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="23"/>
-      <c r="H58" s="23"/>
-      <c r="I58" s="25"/>
-      <c r="J58" s="23"/>
-      <c r="K58" s="25"/>
-      <c r="L58" s="23"/>
-      <c r="M58" s="26"/>
-      <c r="N58" s="27"/>
-      <c r="O58" s="5" t="s">
+    <row r="64" spans="1:16" ht="21.75" customHeight="1">
+      <c r="A64" s="17"/>
+      <c r="B64" s="22"/>
+      <c r="C64" s="23"/>
+      <c r="D64" s="23"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="23"/>
+      <c r="G64" s="23"/>
+      <c r="H64" s="23"/>
+      <c r="I64" s="25"/>
+      <c r="J64" s="23"/>
+      <c r="K64" s="25"/>
+      <c r="L64" s="23"/>
+      <c r="M64" s="26"/>
+      <c r="N64" s="27"/>
+      <c r="O64" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="P58" s="46">
-        <f>SUM(G55+K55+M55+I55)</f>
+      <c r="P64" s="32">
+        <f>SUM(G61+K61+M61+I61)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="148.75" customHeight="1">
-      <c r="A59" s="34" t="s">
+    <row r="65" spans="1:16" ht="148.75" customHeight="1">
+      <c r="A65" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="B59" s="35"/>
-      <c r="C59" s="36"/>
-      <c r="D59" s="29" t="s">
+      <c r="B65" s="36"/>
+      <c r="C65" s="37"/>
+      <c r="D65" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="E59" s="37" t="s">
+      <c r="E65" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="F59" s="38"/>
-      <c r="G59" s="39"/>
-      <c r="H59" s="17"/>
-      <c r="I59" s="17"/>
-      <c r="J59" s="30" t="s">
+      <c r="F65" s="39"/>
+      <c r="G65" s="40"/>
+      <c r="H65" s="17"/>
+      <c r="I65" s="17"/>
+      <c r="J65" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="K59" s="17"/>
-      <c r="L59" s="17"/>
-      <c r="M59" s="31"/>
-      <c r="N59" s="17"/>
-      <c r="O59" s="17"/>
-      <c r="P59" s="17"/>
+      <c r="K65" s="17"/>
+      <c r="L65" s="17"/>
+      <c r="M65" s="31"/>
+      <c r="N65" s="17"/>
+      <c r="O65" s="17"/>
+      <c r="P65" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="O5:P5"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="E65:G65"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
@@ -2836,7 +2944,7 @@
     <mergeCell ref="J5:K5"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="M57:M58 M7:M55">
+  <conditionalFormatting sqref="M63:M64 M7:M61">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
